--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E5A952E-31B0-4C71-820B-CFF381AF769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B4907-966A-411F-AAF1-383728FCB61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>section</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Nationwide</t>
   </si>
   <si>
-    <t>girls-football,</t>
-  </si>
-  <si>
     <t>tournament-football</t>
   </si>
   <si>
@@ -104,14 +101,14 @@
     <t>sessional-football</t>
   </si>
   <si>
-    <t>Girls football team</t>
+    <t>A Girls team run by Will Crowe and we play in the North Wilts Youth Football League. We were established as a team in 2023. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +242,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -588,9 +591,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -977,6 +981,7 @@
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="27.44140625" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1008,9 +1013,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>2013</v>
@@ -1030,8 +1035,8 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
@@ -1310,7 +1315,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2">
         <v>2000</v>
@@ -1324,7 +1329,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>2001</v>
@@ -1349,7 +1354,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>2003</v>
@@ -1360,7 +1365,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>2004</v>
@@ -1371,7 +1376,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>2005</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797B4907-966A-411F-AAF1-383728FCB61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D454C077-5EBA-42BC-B149-93F15C548DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -101,7 +101,7 @@
     <t>sessional-football</t>
   </si>
   <si>
-    <t>A Girls team run by Will Crowe and we play in the North Wilts Youth Football League. We were established as a team in 2023. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+    <t>A Girls team run by Will Crowe. Established in 2023, this team play in the North Wilts Youth Football League. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D454C077-5EBA-42BC-B149-93F15C548DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B431370C-A766-4A46-8E74-420865310AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>section</t>
   </si>
@@ -102,13 +102,25 @@
   </si>
   <si>
     <t>A Girls team run by Will Crowe. Established in 2023, this team play in the North Wilts Youth Football League. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+  </si>
+  <si>
+    <t>Warriors</t>
+  </si>
+  <si>
+    <t>Chris Blackwell</t>
+  </si>
+  <si>
+    <t>wyfc.warriors@gmail.com</t>
+  </si>
+  <si>
+    <t>Boys team. Plays in NWYFL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +260,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -547,7 +567,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -590,13 +610,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -630,6 +652,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1043,7 +1066,33 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E3" s="1"/>
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>2013</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="1">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
@@ -1253,6 +1302,9 @@
       <c r="E72" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B431370C-A766-4A46-8E74-420865310AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969CDE9C-1771-4A1B-BB78-9A4C0C77B955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>section</t>
   </si>
@@ -113,14 +113,47 @@
     <t>wyfc.warriors@gmail.com</t>
   </si>
   <si>
-    <t>Boys team. Plays in NWYFL</t>
+    <t>Panthers</t>
+  </si>
+  <si>
+    <t>Stephen de Oliveria</t>
+  </si>
+  <si>
+    <t>Tuesday 18.3</t>
+  </si>
+  <si>
+    <t>Thursday 18:00</t>
+  </si>
+  <si>
+    <t>Panthers is a team for boys and girls playing in the North Wilts FA Red Development League</t>
+  </si>
+  <si>
+    <t>wyfc.panthers@gmail.com</t>
+  </si>
+  <si>
+    <t>Warriors is a team for boys and girls, playing in the North Wilts Youth Football U12 Division 5 League</t>
+  </si>
+  <si>
+    <t>Rhinos</t>
+  </si>
+  <si>
+    <t>Rob King</t>
+  </si>
+  <si>
+    <t>Tuesday evenings</t>
+  </si>
+  <si>
+    <t>The Under 8 Rhinos is a team for boys and girls.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	wyfc.rhinos@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,18 +289,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -610,13 +662,16 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -996,14 +1051,14 @@
   <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="19.21875" customWidth="1"/>
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1029,14 +1084,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1049,8 +1104,8 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
-        <v>18.3</v>
+      <c r="E2" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1058,7 +1113,7 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I2" t="s">
@@ -1087,18 +1142,70 @@
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>2017</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E4" s="1"/>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E5" s="1"/>
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>2017</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E6" s="1"/>
@@ -1304,8 +1411,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969CDE9C-1771-4A1B-BB78-9A4C0C77B955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B8B697-5581-41C3-A33D-607FE3E4BA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>section</t>
   </si>
@@ -101,9 +101,6 @@
     <t>sessional-football</t>
   </si>
   <si>
-    <t>A Girls team run by Will Crowe. Established in 2023, this team play in the North Wilts Youth Football League. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
-  </si>
-  <si>
     <t>Warriors</t>
   </si>
   <si>
@@ -147,6 +144,66 @@
   </si>
   <si>
     <t xml:space="preserve">	wyfc.rhinos@gmail.com</t>
+  </si>
+  <si>
+    <t>Blackcats</t>
+  </si>
+  <si>
+    <t>Ellie Stratford</t>
+  </si>
+  <si>
+    <t>Tuesdays 18:00</t>
+  </si>
+  <si>
+    <t>Established in 2023, this team play in the North Wilts Youth Football League. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new girls team, formed in 2026.	</t>
+  </si>
+  <si>
+    <t>wyfc.blackcats@gmail.com</t>
+  </si>
+  <si>
+    <t>Rams</t>
+  </si>
+  <si>
+    <t>Lisa Coe &amp; Adam Rutter</t>
+  </si>
+  <si>
+    <t>Rams is a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
+  </si>
+  <si>
+    <t>wyfc.rams@gmail.com</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Stuart Beggs</t>
+  </si>
+  <si>
+    <t>wyfc.rangers01@gmail.com</t>
+  </si>
+  <si>
+    <t>Rangers is a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
+  </si>
+  <si>
+    <t>Tuesdays 17.30</t>
+  </si>
+  <si>
+    <t>Rockets</t>
+  </si>
+  <si>
+    <t>Dave Salter</t>
+  </si>
+  <si>
+    <t>Rockets is a team for boys and girls, playing in the North Wilts Youth Football U10 Development Red League</t>
+  </si>
+  <si>
+    <t>wyfc.rockets@gmail.com</t>
+  </si>
+  <si>
+    <t>Thursday evenings</t>
   </si>
 </sst>
 </file>
@@ -668,10 +725,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1058,8 +1123,8 @@
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -1091,7 +1156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1105,7 +1170,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1114,13 +1179,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="I2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1128,10 +1193,10 @@
         <v>2013</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
       </c>
       <c r="E3" s="1">
         <v>19</v>
@@ -1143,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1157,13 +1222,13 @@
         <v>2017</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
@@ -1172,13 +1237,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1186,13 +1251,13 @@
         <v>2017</v>
       </c>
       <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -1201,23 +1266,127 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
         <v>40</v>
       </c>
-      <c r="I5" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>2018</v>
+      </c>
+      <c r="C6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E9" s="1"/>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>2016</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>2016</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>2015</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E10" s="1"/>
@@ -1412,18 +1581,14 @@
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
+    <hyperlink ref="I7" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
+    <hyperlink ref="I9" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
-          <x14:formula1>
-            <xm:f>data!$A$1:$A$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>F1:F1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>
             <xm:f>data!$C$1:$C$7</xm:f>
@@ -1441,6 +1606,12 @@
             <xm:f>data!$G$1:$G$3</xm:f>
           </x14:formula1>
           <xm:sqref>G1:G1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
+          <x14:formula1>
+            <xm:f>data!$A$1:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>F1:F16 F18:F1048576 I8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B8B697-5581-41C3-A33D-607FE3E4BA73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444BA199-DCE8-49B7-A420-7FE258EA3D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="93">
   <si>
     <t>section</t>
   </si>
@@ -185,9 +185,6 @@
     <t>wyfc.rangers01@gmail.com</t>
   </si>
   <si>
-    <t>Rangers is a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
-  </si>
-  <si>
     <t>Tuesdays 17.30</t>
   </si>
   <si>
@@ -204,6 +201,105 @@
   </si>
   <si>
     <t>Thursday evenings</t>
+  </si>
+  <si>
+    <t>Dragons</t>
+  </si>
+  <si>
+    <t>Martin Speakman</t>
+  </si>
+  <si>
+    <t>wyfc.dragons@gmail.com</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Michaal Webb &amp; Holly Mills</t>
+  </si>
+  <si>
+    <t>Lightning is a team for boys and girls, playing in the North Wilts Youth Football U11 Development Purple League</t>
+  </si>
+  <si>
+    <t>wyfc.lightning@gmail.com</t>
+  </si>
+  <si>
+    <t>Foxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehdi </t>
+  </si>
+  <si>
+    <t>wyfc.foxes@gmail.com</t>
+  </si>
+  <si>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Thunder is a team for boys and girls, playing in the North Wilts Youth Football U11 Development Red League</t>
+  </si>
+  <si>
+    <t>Paul Whitewood</t>
+  </si>
+  <si>
+    <t>wyfc.thunder@gmail.com</t>
+  </si>
+  <si>
+    <t>Wookies</t>
+  </si>
+  <si>
+    <t>Scott Bailey</t>
+  </si>
+  <si>
+    <t>wyfc.wookies@gmail.com</t>
+  </si>
+  <si>
+    <t>Witches</t>
+  </si>
+  <si>
+    <t>Chris Burridge</t>
+  </si>
+  <si>
+    <t>wyfc.witches@gmail.com</t>
+  </si>
+  <si>
+    <t>Wrens</t>
+  </si>
+  <si>
+    <t>Chris Burridge &amp; Natasha Burridge</t>
+  </si>
+  <si>
+    <t>wyfc.wrens@gmail.com</t>
+  </si>
+  <si>
+    <t>Ravens</t>
+  </si>
+  <si>
+    <t>Craig Jones &amp; Natasha James</t>
+  </si>
+  <si>
+    <t>The Wrens are a team for girls, playing in the North Wilts Youth Football U14 Division 5 League</t>
+  </si>
+  <si>
+    <t>The Ravens are a team for girls, playing in the North Wilts Football U14 Division 6 League.</t>
+  </si>
+  <si>
+    <t>The Witches are a team for girls, playing in the North Wilts Youth Football U13 Division 1 Girls League</t>
+  </si>
+  <si>
+    <t>The Wookies are a team for boys and girls, playing in the North Wilts Youth Football U12 Division 2 League</t>
+  </si>
+  <si>
+    <t>The Foxes are a team for boys and girls, playing in the North Wilts Youth Football U11 Development Red League</t>
+  </si>
+  <si>
+    <t>The Dragons are a team for boys and girls, playing in the North Wilts Youth Football U11 Development Blue League</t>
+  </si>
+  <si>
+    <t>The Rangers are a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
+  </si>
+  <si>
+    <t>wyfc.ravens@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -721,7 +817,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -737,6 +833,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1119,7 +1216,7 @@
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
     <col min="3" max="3" width="19.21875" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
@@ -1344,7 +1441,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -1353,7 +1450,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
         <v>53</v>
@@ -1367,13 +1464,13 @@
         <v>2015</v>
       </c>
       <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
       </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1382,79 +1479,287 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>2014</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>2014</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>2014</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>2014</v>
+      </c>
+      <c r="C13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>2013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>2012</v>
+      </c>
+      <c r="C15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>2010</v>
+      </c>
+      <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>2010</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.3">
@@ -1583,9 +1888,16 @@
     <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
     <hyperlink ref="I7" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
     <hyperlink ref="I9" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
+    <hyperlink ref="I10" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
+    <hyperlink ref="I11" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
+    <hyperlink ref="I13" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
+    <hyperlink ref="I14" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
+    <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
+    <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
+    <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444BA199-DCE8-49B7-A420-7FE258EA3D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EF8CC2C-F61A-432E-BD1E-3CE3567A1AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
   <si>
     <t>section</t>
   </si>
@@ -300,6 +300,39 @@
   </si>
   <si>
     <t>wyfc.ravens@gmail.com</t>
+  </si>
+  <si>
+    <t>Mens</t>
+  </si>
+  <si>
+    <t>Paul Brown</t>
+  </si>
+  <si>
+    <t>Wednesdays</t>
+  </si>
+  <si>
+    <t>The Men's team is a senior team playing in the Swindon and District Community Football League</t>
+  </si>
+  <si>
+    <t>wyfc.chair@gmail.com</t>
+  </si>
+  <si>
+    <t>Ability-Counts</t>
+  </si>
+  <si>
+    <t>tbc</t>
+  </si>
+  <si>
+    <t>an exciting new Ability-Counts team - Established May 2026</t>
+  </si>
+  <si>
+    <t>Wildcats</t>
+  </si>
+  <si>
+    <t>Tuesday evenings 6pm</t>
+  </si>
+  <si>
+    <t>Free weekly sessional football for girls ages 6 to 8. Come along and join-in for free</t>
   </si>
 </sst>
 </file>
@@ -1718,13 +1751,82 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E20" s="1"/>
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E21" s="1"/>
@@ -1895,9 +1997,12 @@
     <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
     <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
     <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
+    <hyperlink ref="I18" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
+    <hyperlink ref="I19" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
+    <hyperlink ref="I20" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId15"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -1909,7 +2014,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3A402E24-C34D-416E-85F6-ACAE2E15BCE1}">
           <x14:formula1>
-            <xm:f>data!$E$1:$E$32</xm:f>
+            <xm:f>data!$E$2:$E$33</xm:f>
           </x14:formula1>
           <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EF8CC2C-F61A-432E-BD1E-3CE3567A1AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CBDCD7-1671-4586-97EE-C1E08772544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="132">
   <si>
     <t>section</t>
   </si>
@@ -333,6 +333,90 @@
   </si>
   <si>
     <t>Free weekly sessional football for girls ages 6 to 8. Come along and join-in for free</t>
+  </si>
+  <si>
+    <t>Lions</t>
+  </si>
+  <si>
+    <t>David Scott</t>
+  </si>
+  <si>
+    <t>Tuesday Evenings</t>
+  </si>
+  <si>
+    <t>The Lions are is a team for boys and girls, playing in the North Wilts Youth Football U13 Division 4 League</t>
+  </si>
+  <si>
+    <t>wyfc.lions@gmail.com</t>
+  </si>
+  <si>
+    <t>Wasps</t>
+  </si>
+  <si>
+    <t>Reece Kewley &amp; Jack Kewley</t>
+  </si>
+  <si>
+    <t>wyfc.wasps@gmail.com</t>
+  </si>
+  <si>
+    <t>Wolves</t>
+  </si>
+  <si>
+    <t>Ian Porter</t>
+  </si>
+  <si>
+    <t>Monday Evenings</t>
+  </si>
+  <si>
+    <t>The Wolves are a team for boys and girls, playing in the North Wilts Youth Football U13 Division 4 League</t>
+  </si>
+  <si>
+    <t>Wasps is a team for boys and girls, playing in the North Wilts Youth Football U13 Division 5 League</t>
+  </si>
+  <si>
+    <t>wyfc.wolves@gmail.com</t>
+  </si>
+  <si>
+    <t>Hurricanes</t>
+  </si>
+  <si>
+    <t>David Mills</t>
+  </si>
+  <si>
+    <t>Wednesday Evenings</t>
+  </si>
+  <si>
+    <t>The Hurricanes are a team for boys and girls, playing in the North Wilts Youth Football U14 Division 1 League</t>
+  </si>
+  <si>
+    <t>wyfc.hurricanes@gmail.com</t>
+  </si>
+  <si>
+    <t>Tornadoes</t>
+  </si>
+  <si>
+    <t>Darren Harvey</t>
+  </si>
+  <si>
+    <t>The Tornadoes a team for boys and girls, playing in the North Wilts Youth Football U14 Division 4 League</t>
+  </si>
+  <si>
+    <t>wyfc.tornadoes@gmail.com</t>
+  </si>
+  <si>
+    <t>Silverbacks</t>
+  </si>
+  <si>
+    <t>Sean Millwaters</t>
+  </si>
+  <si>
+    <t>Thursday Evenings</t>
+  </si>
+  <si>
+    <t>The Silverbacks are  a team for boys and girls, playing in the North Wilts Youth Football U15 Division 2 League</t>
+  </si>
+  <si>
+    <t>wyfc.silverbacks@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -1828,23 +1912,179 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E21" s="1"/>
+    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>2011</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E26" s="1"/>
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>2011</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>2011</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>2010</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>2010</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>2009</v>
+      </c>
+      <c r="C26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E27" s="1"/>
@@ -2000,9 +2240,15 @@
     <hyperlink ref="I18" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
     <hyperlink ref="I19" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
     <hyperlink ref="I20" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
+    <hyperlink ref="I21" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
+    <hyperlink ref="I22" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
+    <hyperlink ref="I23" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
+    <hyperlink ref="I24" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
+    <hyperlink ref="I25" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
+    <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId21"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CBDCD7-1671-4586-97EE-C1E08772544F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F081D620-3200-4899-AC31-77C735296C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -1917,7 +1917,7 @@
         <v>23</v>
       </c>
       <c r="B21">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C21" t="s">
         <v>104</v>
@@ -1946,7 +1946,7 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C22" t="s">
         <v>109</v>
@@ -1975,7 +1975,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C23" t="s">
         <v>112</v>
@@ -2004,7 +2004,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C24" t="s">
         <v>118</v>
@@ -2033,7 +2033,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C25" t="s">
         <v>123</v>
@@ -2062,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="B26">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C26" t="s">
         <v>127</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F081D620-3200-4899-AC31-77C735296C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A859-8CA6-4A39-B6D7-2DABED929EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="140">
   <si>
     <t>section</t>
   </si>
@@ -417,6 +417,30 @@
   </si>
   <si>
     <t>wyfc.silverbacks@gmail.com</t>
+  </si>
+  <si>
+    <t>Broncos</t>
+  </si>
+  <si>
+    <t>Rob Zukovic</t>
+  </si>
+  <si>
+    <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football U16 Division 3 League</t>
+  </si>
+  <si>
+    <t>wyfc.broncos@gmail.com</t>
+  </si>
+  <si>
+    <t>u18</t>
+  </si>
+  <si>
+    <t>Elliot Woodhead &amp; Sean Mason</t>
+  </si>
+  <si>
+    <t>The Under 18 is a team for young people, playing in the North Wilts Youth Football U17/18 Division 1 League</t>
+  </si>
+  <si>
+    <t>wroughtonyouthfc@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -934,7 +958,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -951,6 +975,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1370,21 +1395,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="106.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1392,40 +1417,40 @@
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>44</v>
+      <c r="H2" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>2013</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>28</v>
+      <c r="H3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1486,36 +1511,36 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B6">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1523,71 +1548,71 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="H7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1596,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
@@ -1610,10 +1635,10 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>38</v>
@@ -1625,13 +1650,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1639,10 +1664,10 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>38</v>
@@ -1654,13 +1679,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1668,10 +1693,10 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>38</v>
@@ -1682,11 +1707,11 @@
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>69</v>
+      <c r="H12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1694,13 +1719,13 @@
         <v>23</v>
       </c>
       <c r="B13">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>38</v>
@@ -1712,13 +1737,13 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1726,13 +1751,13 @@
         <v>2013</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
+      </c>
+      <c r="E14" s="1">
+        <v>19</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
@@ -1740,11 +1765,11 @@
       <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>88</v>
+      <c r="H14" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -2086,11 +2111,63 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E27" s="1"/>
+    <row r="27" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27">
+        <v>2009</v>
+      </c>
+      <c r="C27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="E28" s="1"/>
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28">
+        <v>2007</v>
+      </c>
+      <c r="C28" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
@@ -2226,14 +2303,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+    <hyperlink ref="I14" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
-    <hyperlink ref="I7" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
-    <hyperlink ref="I9" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
-    <hyperlink ref="I10" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
-    <hyperlink ref="I11" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
-    <hyperlink ref="I13" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
-    <hyperlink ref="I14" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
+    <hyperlink ref="I8" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
+    <hyperlink ref="I9" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
+    <hyperlink ref="I10" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
+    <hyperlink ref="I12" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
+    <hyperlink ref="I13" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
     <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
     <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
     <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
@@ -2246,35 +2323,37 @@
     <hyperlink ref="I24" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
     <hyperlink ref="I25" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
     <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
+    <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
+    <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId23"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
+          <x14:formula1>
+            <xm:f>data!$A$1:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>F18:F1048576 I7 F1:F5 F6:F16</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>
             <xm:f>data!$C$1:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A1048576</xm:sqref>
+          <xm:sqref>A1:A5 A6:A1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3A402E24-C34D-416E-85F6-ACAE2E15BCE1}">
           <x14:formula1>
             <xm:f>data!$E$2:$E$33</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
+          <xm:sqref>B1:B5 B6:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B8CC80F3-8A5F-4A97-9C2A-582813DC8A38}">
           <x14:formula1>
             <xm:f>data!$G$1:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G1:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
-          <x14:formula1>
-            <xm:f>data!$A$1:$A$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>F1:F16 F18:F1048576 I8</xm:sqref>
+          <xm:sqref>G1:G5 G6:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A859-8CA6-4A39-B6D7-2DABED929EA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B4FD39-0A36-4E5F-9924-04D188848FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -122,9 +122,6 @@
     <t>Thursday 18:00</t>
   </si>
   <si>
-    <t>Panthers is a team for boys and girls playing in the North Wilts FA Red Development League</t>
-  </si>
-  <si>
     <t>wyfc.panthers@gmail.com</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>Tuesday evenings</t>
   </si>
   <si>
-    <t>The Under 8 Rhinos is a team for boys and girls.</t>
-  </si>
-  <si>
     <t xml:space="preserve">	wyfc.rhinos@gmail.com</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>Lisa Coe &amp; Adam Rutter</t>
   </si>
   <si>
-    <t>Rams is a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
-  </si>
-  <si>
     <t>wyfc.rams@gmail.com</t>
   </si>
   <si>
@@ -194,9 +185,6 @@
     <t>Dave Salter</t>
   </si>
   <si>
-    <t>Rockets is a team for boys and girls, playing in the North Wilts Youth Football U10 Development Red League</t>
-  </si>
-  <si>
     <t>wyfc.rockets@gmail.com</t>
   </si>
   <si>
@@ -441,6 +429,18 @@
   </si>
   <si>
     <t>wroughtonyouthfc@gmail.com</t>
+  </si>
+  <si>
+    <t>The Panthers are a team for boys and girls playing in the North Wilts FA Red Development League</t>
+  </si>
+  <si>
+    <t>The Rhinos are a team for boys and girls.</t>
+  </si>
+  <si>
+    <t>The Rams are a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
+  </si>
+  <si>
+    <t>The Rockets are a team for boys and girls, playing in the North Wilts Youth Football U10 Development Red League</t>
   </si>
 </sst>
 </file>
@@ -1403,13 +1403,13 @@
         <v>2018</v>
       </c>
       <c r="C2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1418,10 +1418,10 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="106.2" x14ac:dyDescent="0.3">
@@ -1447,13 +1447,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1476,10 +1476,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
@@ -1490,13 +1490,13 @@
         <v>2017</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -1505,10 +1505,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1519,13 +1519,13 @@
         <v>2016</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1534,10 +1534,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
@@ -1548,13 +1548,13 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1563,10 +1563,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="42" x14ac:dyDescent="0.3">
@@ -1577,13 +1577,13 @@
         <v>2015</v>
       </c>
       <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1592,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
@@ -1606,13 +1606,13 @@
         <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1621,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
@@ -1635,13 +1635,13 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1650,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="42" x14ac:dyDescent="0.3">
@@ -1664,13 +1664,13 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -1679,10 +1679,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1693,13 +1693,13 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1722,13 +1722,13 @@
         <v>2013</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1737,10 +1737,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1766,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>28</v>
@@ -1780,13 +1780,13 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1809,13 +1809,13 @@
         <v>2010</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1824,10 +1824,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1838,13 +1838,13 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1853,10 +1853,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1864,13 +1864,13 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1879,10 +1879,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1890,13 +1890,13 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1905,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1916,13 +1916,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -1945,13 +1945,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1974,13 +1974,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -1989,10 +1989,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2003,13 +2003,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2032,13 +2032,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2061,13 +2061,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2076,10 +2076,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2090,13 +2090,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -2105,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2119,13 +2119,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -2134,10 +2134,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -2148,13 +2148,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -2163,10 +2163,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B4FD39-0A36-4E5F-9924-04D188848FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC57CDE0-19D1-44C1-A97C-78C248B6677B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
   <si>
     <t>section</t>
   </si>
@@ -441,6 +441,18 @@
   </si>
   <si>
     <t>The Rockets are a team for boys and girls, playing in the North Wilts Youth Football U10 Development Red League</t>
+  </si>
+  <si>
+    <t>sponsorName</t>
+  </si>
+  <si>
+    <t>sponsorLogo</t>
+  </si>
+  <si>
+    <t>sponsorDescription</t>
+  </si>
+  <si>
+    <t>sponsorURL</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -1364,9 +1376,13 @@
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="36.88671875" style="3" customWidth="1"/>
     <col min="9" max="9" width="29.109375" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1394,8 +1410,20 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1452,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="106.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1453,7 +1481,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1482,7 +1510,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1511,7 +1539,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1540,7 +1568,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1569,7 +1597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1598,7 +1626,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1627,7 +1655,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1656,7 +1684,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1685,7 +1713,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1714,7 +1742,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1743,7 +1771,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1772,7 +1800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1801,7 +1829,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC57CDE0-19D1-44C1-A97C-78C248B6677B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F13D60-A7B9-4778-8574-44CE8987E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -20,8 +20,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="147">
   <si>
     <t>section</t>
   </si>
@@ -453,6 +475,15 @@
   </si>
   <si>
     <t>sponsorURL</t>
+  </si>
+  <si>
+    <t>Ocean Escape</t>
+  </si>
+  <si>
+    <t>Best holiday let in North Devon</t>
+  </si>
+  <si>
+    <t>http://oceanescape.co.uk</t>
   </si>
 </sst>
 </file>
@@ -1045,6 +1076,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1480,6 +1575,18 @@
       <c r="I3" t="s">
         <v>13</v>
       </c>
+      <c r="J3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -2353,9 +2460,10 @@
     <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
     <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
     <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
+    <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId24"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F13D60-A7B9-4778-8574-44CE8987E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9627362D-8063-4CE4-A1FE-83BCBBC8106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -20,30 +20,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
   <si>
     <t>section</t>
   </si>
@@ -484,6 +462,9 @@
   </si>
   <si>
     <t>http://oceanescape.co.uk</t>
+  </si>
+  <si>
+    <t>ocean.png</t>
   </si>
 </sst>
 </file>
@@ -1076,70 +1057,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1578,8 +1495,8 @@
       <c r="J3" t="s">
         <v>144</v>
       </c>
-      <c r="K3" t="e" vm="1">
-        <v>#VALUE!</v>
+      <c r="K3" t="s">
+        <v>147</v>
       </c>
       <c r="L3" t="s">
         <v>145</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9627362D-8063-4CE4-A1FE-83BCBBC8106F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91297F99-855A-4169-9A90-6626229F41B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -464,7 +464,7 @@
     <t>http://oceanescape.co.uk</t>
   </si>
   <si>
-    <t>ocean.png</t>
+    <t>/images/sponsors/ocean.png</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1389,7 @@
     <col min="8" max="8" width="36.88671875" style="3" customWidth="1"/>
     <col min="9" max="9" width="29.109375" customWidth="1"/>
     <col min="10" max="10" width="23.33203125" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="11" max="11" width="35.6640625" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="16.77734375" customWidth="1"/>
   </cols>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91297F99-855A-4169-9A90-6626229F41B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B43715-FF72-4333-A03C-DEA6C0424303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -116,9 +116,6 @@
     <t>Stephen de Oliveria</t>
   </si>
   <si>
-    <t>Tuesday 18.3</t>
-  </si>
-  <si>
     <t>Thursday 18:00</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Tuesdays 18:00</t>
   </si>
   <si>
-    <t>Established in 2023, this team play in the North Wilts Youth Football League. Will is supported by 2 coaching volunteers (Kyle and Alex) and all 3 have daughters that play in the team. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
-  </si>
-  <si>
     <t xml:space="preserve">A new girls team, formed in 2026.	</t>
   </si>
   <si>
@@ -465,6 +459,12 @@
   </si>
   <si>
     <t>/images/sponsors/ocean.png</t>
+  </si>
+  <si>
+    <t>Established in 2023, this team play in the North Wilts Youth Football League. If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+  </si>
+  <si>
+    <t>Tuesday 18.30</t>
   </si>
 </sst>
 </file>
@@ -1390,8 +1390,8 @@
     <col min="9" max="9" width="29.109375" customWidth="1"/>
     <col min="10" max="10" width="23.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1423,16 +1423,16 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L1" t="s">
         <v>140</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>141</v>
-      </c>
-      <c r="L1" t="s">
-        <v>142</v>
-      </c>
-      <c r="M1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1443,13 +1443,13 @@
         <v>2018</v>
       </c>
       <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1458,13 +1458,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="106.2" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1487,22 +1487,22 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" t="s">
+        <v>143</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="K3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
@@ -1528,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
@@ -1542,13 +1542,13 @@
         <v>2017</v>
       </c>
       <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
@@ -1557,10 +1557,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1571,13 +1571,13 @@
         <v>2016</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -1586,10 +1586,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1600,13 +1600,13 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1615,10 +1615,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" x14ac:dyDescent="0.3">
@@ -1629,13 +1629,13 @@
         <v>2015</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1644,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1658,13 +1658,13 @@
         <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>15</v>
@@ -1673,10 +1673,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1687,13 +1687,13 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
         <v>15</v>
@@ -1702,10 +1702,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.3">
@@ -1716,13 +1716,13 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -1731,10 +1731,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1745,13 +1745,13 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
         <v>66</v>
       </c>
-      <c r="D12" t="s">
-        <v>68</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>15</v>
@@ -1760,10 +1760,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1774,13 +1774,13 @@
         <v>2013</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
         <v>15</v>
@@ -1789,10 +1789,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>28</v>
@@ -1832,13 +1832,13 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -1847,10 +1847,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1861,13 +1861,13 @@
         <v>2010</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1876,10 +1876,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1890,13 +1890,13 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1905,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1916,13 +1916,13 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1931,10 +1931,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1942,13 +1942,13 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1957,10 +1957,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1968,13 +1968,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -1997,13 +1997,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2026,13 +2026,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2041,10 +2041,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2055,13 +2055,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2070,10 +2070,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2084,13 +2084,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2099,10 +2099,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2113,13 +2113,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2128,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2142,13 +2142,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="D26" t="s">
-        <v>124</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -2157,10 +2157,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2171,13 +2171,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -2186,10 +2186,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -2200,13 +2200,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -2215,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B43715-FF72-4333-A03C-DEA6C0424303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981693B2-BECF-4627-99B7-9416C62F50E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -452,9 +452,6 @@
     <t>Ocean Escape</t>
   </si>
   <si>
-    <t>Best holiday let in North Devon</t>
-  </si>
-  <si>
     <t>http://oceanescape.co.uk</t>
   </si>
   <si>
@@ -465,6 +462,10 @@
   </si>
   <si>
     <t>Tuesday 18.30</t>
+  </si>
+  <si>
+    <t>Ocean Escape is the perfect, modern, holiday home for families or celebration events. Situated in the stunning coastal seaside village of Westward Ho ! in North Devon.
+We are Proud to be supporting grassroots girls football – Go Magic !!</t>
   </si>
 </sst>
 </file>
@@ -982,7 +983,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1000,6 +1001,9 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1464,7 +1468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1478,7 +1482,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1487,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
@@ -1496,13 +1500,13 @@
         <v>142</v>
       </c>
       <c r="K3" t="s">
-        <v>145</v>
-      </c>
-      <c r="L3" t="s">
+        <v>144</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981693B2-BECF-4627-99B7-9416C62F50E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFF71A4-3E28-4A66-843D-73F832BE73D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -446,9 +446,6 @@
     <t>sponsorDescription</t>
   </si>
   <si>
-    <t>sponsorURL</t>
-  </si>
-  <si>
     <t>Ocean Escape</t>
   </si>
   <si>
@@ -464,8 +461,11 @@
     <t>Tuesday 18.30</t>
   </si>
   <si>
+    <t>sponsorUrl</t>
+  </si>
+  <si>
     <t>Ocean Escape is the perfect, modern, holiday home for families or celebration events. Situated in the stunning coastal seaside village of Westward Ho ! in North Devon.
-We are Proud to be supporting grassroots girls football – Go Magic !!</t>
+We are Proud to be supporting grassroots girls football  ….. Go Magic !!</t>
   </si>
 </sst>
 </file>
@@ -1436,7 +1436,7 @@
         <v>140</v>
       </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1468,7 +1468,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1491,22 +1491,22 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>147</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFF71A4-3E28-4A66-843D-73F832BE73D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C989F0F-7CA9-48AB-A49E-9BB5825D4BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -20,8 +20,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>William Crowe</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{29A9FAE4-E562-48D1-898F-AACF01903855}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crowe:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="151">
   <si>
     <t>section</t>
   </si>
@@ -146,9 +180,6 @@
     <t>Tuesdays 18:00</t>
   </si>
   <si>
-    <t xml:space="preserve">A new girls team, formed in 2026.	</t>
-  </si>
-  <si>
     <t>wyfc.blackcats@gmail.com</t>
   </si>
   <si>
@@ -446,9 +477,6 @@
     <t>sponsorDescription</t>
   </si>
   <si>
-    <t>Ocean Escape</t>
-  </si>
-  <si>
     <t>http://oceanescape.co.uk</t>
   </si>
   <si>
@@ -464,15 +492,30 @@
     <t>sponsorUrl</t>
   </si>
   <si>
-    <t>Ocean Escape is the perfect, modern, holiday home for families or celebration events. Situated in the stunning coastal seaside village of Westward Ho ! in North Devon.
-We are Proud to be supporting grassroots girls football  ….. Go Magic !!</t>
+    <t>A new girls team, formed in 2026.	 If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+  </si>
+  <si>
+    <t>Hannah McDanielson</t>
+  </si>
+  <si>
+    <t>/images/sponsors/hannah.webp</t>
+  </si>
+  <si>
+    <t>https://hannahmcdanielsonjewellery.co.uk/</t>
+  </si>
+  <si>
+    <t>Unique bespoke jewellery. Designed for life, created with care.
+Sentimental jewellery that celebrates your story.</t>
+  </si>
+  <si>
+    <t>Ocean Escape.co.uk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,6 +683,31 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="29"/>
+      <color rgb="FF0A0F0E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0F0E"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -983,7 +1051,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1002,7 +1070,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1379,7 +1453,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
   <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1395,7 +1469,7 @@
     <col min="10" max="10" width="23.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" customWidth="1"/>
+    <col min="13" max="13" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1427,19 +1501,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" t="s">
         <v>138</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>139</v>
       </c>
-      <c r="L1" t="s">
-        <v>140</v>
-      </c>
       <c r="M1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="69" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1462,13 +1536,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="M2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1482,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1491,22 +1577,20 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" t="s">
         <v>141</v>
       </c>
-      <c r="K3" t="s">
-        <v>143</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>147</v>
-      </c>
+      <c r="L3" s="9"/>
       <c r="M3" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -1532,11 +1616,12 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1561,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
@@ -1575,10 +1660,10 @@
         <v>2016</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>40</v>
@@ -1590,10 +1675,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1604,13 +1689,13 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
         <v>46</v>
       </c>
-      <c r="D7" t="s">
-        <v>47</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1619,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" x14ac:dyDescent="0.3">
@@ -1633,13 +1718,13 @@
         <v>2015</v>
       </c>
       <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
         <v>15</v>
@@ -1648,10 +1733,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1662,10 +1747,10 @@
         <v>2014</v>
       </c>
       <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
         <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -1677,10 +1762,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
@@ -1691,10 +1776,10 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
         <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>36</v>
@@ -1706,10 +1791,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.3">
@@ -1720,10 +1805,10 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
         <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
@@ -1735,10 +1820,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1749,10 +1834,10 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>36</v>
@@ -1764,10 +1849,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1778,10 +1863,10 @@
         <v>2013</v>
       </c>
       <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
         <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>36</v>
@@ -1793,10 +1878,10 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1836,10 +1921,10 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" t="s">
         <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>36</v>
@@ -1851,10 +1936,10 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1865,13 +1950,13 @@
         <v>2010</v>
       </c>
       <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
         <v>74</v>
       </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1880,10 +1965,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1894,13 +1979,13 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
         <v>77</v>
       </c>
-      <c r="D17" t="s">
-        <v>78</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -1909,10 +1994,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1920,13 +2005,13 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
         <v>87</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
@@ -1935,10 +2020,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1946,13 +2031,13 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1961,10 +2046,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
@@ -1972,13 +2057,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1987,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -2001,13 +2086,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -2016,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2030,13 +2115,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
         <v>103</v>
       </c>
-      <c r="D22" t="s">
-        <v>104</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2045,10 +2130,10 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2059,13 +2144,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
         <v>106</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2074,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2088,13 +2173,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
         <v>112</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2103,10 +2188,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2117,13 +2202,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2132,10 +2217,10 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2146,13 +2231,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" t="s">
         <v>121</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -2161,10 +2246,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
@@ -2175,13 +2260,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" t="s">
         <v>126</v>
       </c>
-      <c r="D27" t="s">
-        <v>127</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -2190,10 +2275,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -2204,13 +2289,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" t="s">
         <v>130</v>
       </c>
-      <c r="D28" t="s">
-        <v>131</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -2219,10 +2304,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -2385,6 +2470,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId24"/>
+  <legacyDrawing r:id="rId25"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C989F0F-7CA9-48AB-A49E-9BB5825D4BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC73E2D-1EDB-4D55-85EB-318B52464CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,12 +50,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crowe:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+ages</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
   <si>
     <t>section</t>
   </si>
@@ -509,6 +533,18 @@
   </si>
   <si>
     <t>Ocean Escape.co.uk</t>
+  </si>
+  <si>
+    <t>A&amp;J Waste Services</t>
+  </si>
+  <si>
+    <t>/images/sponsors/a&amp;j.png</t>
+  </si>
+  <si>
+    <t>https://aandjwasteservices.co.uk/</t>
+  </si>
+  <si>
+    <t>Ocean Escape is the perfect, modern, holiday home for families or celebration events. Situated in the stunning coastal seaside village of Westward Ho ! in North Devon. We are Proud to be supporting grassroots girls football ----- Go Magic !!</t>
   </si>
 </sst>
 </file>
@@ -1588,7 +1624,9 @@
       <c r="K3" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="9"/>
+      <c r="L3" s="9" t="s">
+        <v>154</v>
+      </c>
       <c r="M3" s="2" t="s">
         <v>140</v>
       </c>
@@ -1969,6 +2007,15 @@
       </c>
       <c r="I16" s="2" t="s">
         <v>75</v>
+      </c>
+      <c r="J16" t="s">
+        <v>151</v>
+      </c>
+      <c r="K16" t="s">
+        <v>152</v>
+      </c>
+      <c r="M16" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC73E2D-1EDB-4D55-85EB-318B52464CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA9F16C-01C3-44EE-991B-801D32C17144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>section</t>
   </si>
@@ -545,13 +545,29 @@
   </si>
   <si>
     <t>Ocean Escape is the perfect, modern, holiday home for families or celebration events. Situated in the stunning coastal seaside village of Westward Ho ! in North Devon. We are Proud to be supporting grassroots girls football ----- Go Magic !!</t>
+  </si>
+  <si>
+    <t>We specialise in Materials Management for the Construction, Development and Utility sectors across the UK. With decades of industry knowledge, our highly experienced management team ensure an expert consultancy service is provided to all of our clients. Professional services we provide include Soil Waste Management, CL:AIRE Applications, Waste Classification, Earthworks Projects and Aggregate Supply to a national client base.
+A &amp; J Waste Services Ltd are proud to be members of CL:AIRE and we share in their commitment to sustainable land reuse and development.</t>
+  </si>
+  <si>
+    <t>MJD Mechanical &amp; Electrical Services</t>
+  </si>
+  <si>
+    <t>/images/mjd.png</t>
+  </si>
+  <si>
+    <t>Since 2007, MJD Mechanical &amp; Electrical Services have been leading providers of mechanical, electrical &amp; renewable services across Bristol and the South West. We offer a full design, installation and maintenance service across multiple sectors, including Healthcare, Education, Commercial, Retail, Hotel &amp; Residential &amp; Sport &amp; Leisure, additionally we often undertake various listed, heritage and special purpose projects.</t>
+  </si>
+  <si>
+    <t>https://mjdgroup.co.uk/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -744,6 +760,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1087,7 +1109,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1113,6 +1135,12 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1502,9 +1530,9 @@
     <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="36.88671875" style="3" customWidth="1"/>
     <col min="9" max="9" width="29.109375" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
     <col min="13" max="13" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1979,8 +2007,20 @@
       <c r="I15" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K15" t="s">
+        <v>157</v>
+      </c>
+      <c r="L15" t="s">
+        <v>158</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="285.60000000000002" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2014,11 +2054,14 @@
       <c r="K16" t="s">
         <v>152</v>
       </c>
+      <c r="L16" s="13" t="s">
+        <v>155</v>
+      </c>
       <c r="M16" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2047,7 +2090,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2072,8 +2115,9 @@
       <c r="I18" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2099,7 +2143,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2125,7 +2169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2154,7 +2198,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2183,7 +2227,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2212,7 +2256,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2285,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2270,7 +2314,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2299,7 +2343,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2328,7 +2372,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2357,16 +2401,16 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.3">
@@ -2514,10 +2558,11 @@
     <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
     <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
     <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
+    <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId24"/>
-  <legacyDrawing r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId25"/>
+  <legacyDrawing r:id="rId26"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA9F16C-01C3-44EE-991B-801D32C17144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF74B84D-6B00-49D2-AEDE-389D092EBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Crowe:</t>
         </r>
@@ -43,7 +43,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -58,7 +58,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Crowe:</t>
         </r>
@@ -67,7 +67,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 ages</t>
@@ -554,13 +554,13 @@
     <t>MJD Mechanical &amp; Electrical Services</t>
   </si>
   <si>
-    <t>/images/mjd.png</t>
-  </si>
-  <si>
     <t>Since 2007, MJD Mechanical &amp; Electrical Services have been leading providers of mechanical, electrical &amp; renewable services across Bristol and the South West. We offer a full design, installation and maintenance service across multiple sectors, including Healthcare, Education, Commercial, Retail, Hotel &amp; Residential &amp; Sport &amp; Leisure, additionally we often undertake various listed, heritage and special purpose projects.</t>
   </si>
   <si>
     <t>https://mjdgroup.co.uk/</t>
+  </si>
+  <si>
+    <t>/images/sponsors/mjd.png</t>
   </si>
 </sst>
 </file>
@@ -739,14 +739,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="29"/>
@@ -2011,13 +2011,13 @@
         <v>156</v>
       </c>
       <c r="K15" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" t="s">
         <v>157</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="285.60000000000002" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF74B84D-6B00-49D2-AEDE-389D092EBAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C678ECC4-B776-40E2-A30B-03D31D4DD6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="164">
   <si>
     <t>section</t>
   </si>
@@ -561,6 +561,18 @@
   </si>
   <si>
     <t>/images/sponsors/mjd.png</t>
+  </si>
+  <si>
+    <t>/images/sponsors/headstart.png</t>
+  </si>
+  <si>
+    <t>Head Start Skillz</t>
+  </si>
+  <si>
+    <t>Unlocking Potential, Shaping Futures. We believe that training our young people on critical practical subjects will help to give them a significant head start in life. Whether it’s learning how to manage money and get the most out of their future income, providing first aid to someone in need, remaining safe online and protecting their online identity and data or using their newly acquired self-defence skills to negotiate a tricky situation.</t>
+  </si>
+  <si>
+    <t>https://headstartskillz.com/</t>
   </si>
 </sst>
 </file>
@@ -1862,6 +1874,18 @@
       <c r="I10" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="J10" t="s">
+        <v>161</v>
+      </c>
+      <c r="K10" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" t="s">
+        <v>162</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -2559,10 +2583,11 @@
     <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
     <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
     <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
+    <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId25"/>
-  <legacyDrawing r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId26"/>
+  <legacyDrawing r:id="rId27"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C678ECC4-B776-40E2-A30B-03D31D4DD6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1CEBF0-8840-43DF-91E6-A804395F7BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="164">
   <si>
     <t>section</t>
   </si>
@@ -1121,7 +1121,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1153,6 +1153,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2081,11 +2084,11 @@
       <c r="L16" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2114,7 +2117,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2141,7 +2144,7 @@
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2167,7 +2170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2193,7 +2196,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2222,7 +2225,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2279,8 +2282,20 @@
       <c r="I23" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>151</v>
+      </c>
+      <c r="K23" t="s">
+        <v>152</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="M23" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2309,7 +2324,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2338,7 +2353,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2367,7 +2382,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2396,7 +2411,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2425,16 +2440,16 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.3">
@@ -2584,10 +2599,11 @@
     <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
     <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
     <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
+    <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId26"/>
-  <legacyDrawing r:id="rId27"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId27"/>
+  <legacyDrawing r:id="rId28"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1CEBF0-8840-43DF-91E6-A804395F7BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C78440-795E-4FCC-84A9-8E0DDFC0E695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="168">
   <si>
     <t>section</t>
   </si>
@@ -573,6 +573,20 @@
   </si>
   <si>
     <t>https://headstartskillz.com/</t>
+  </si>
+  <si>
+    <t>/images/sponsors/iew.png</t>
+  </si>
+  <si>
+    <t>Industrial Electronic Wiring Ltd</t>
+  </si>
+  <si>
+    <t>For over 40 years, IEW Ltd. has been a cornerstone of the contract electronics manufacturing industry. With a dedicated team of over 60 professionals, we provide exemplary service to companies specialising in complex machinery.
+We are driven by a dual commitment – delivering cost-effective solutions and ensuring every assembly is delivered to time and rigorously tested, guaranteeing peak quality and reliability.
+Welcome to IEW Ltd. – Where Innovation Meets Commitment.</t>
+  </si>
+  <si>
+    <t>https://www.iew.co.uk/</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1135,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1155,7 +1169,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1547,7 +1564,7 @@
     <col min="9" max="9" width="29.109375" customWidth="1"/>
     <col min="10" max="10" width="30.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
-    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="12" max="12" width="84.6640625" customWidth="1"/>
     <col min="13" max="13" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2254,7 +2271,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2295,7 +2312,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2322,6 +2339,18 @@
       </c>
       <c r="I24" s="2" t="s">
         <v>115</v>
+      </c>
+      <c r="J24" t="s">
+        <v>165</v>
+      </c>
+      <c r="K24" t="s">
+        <v>164</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="M24" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -2352,6 +2381,7 @@
       <c r="I25" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="L25" s="15"/>
     </row>
     <row r="26" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -2381,6 +2411,7 @@
       <c r="I26" s="2" t="s">
         <v>124</v>
       </c>
+      <c r="L26" s="15"/>
     </row>
     <row r="27" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -2410,6 +2441,7 @@
       <c r="I27" s="2" t="s">
         <v>128</v>
       </c>
+      <c r="L27" s="15"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -2439,9 +2471,11 @@
       <c r="I28" s="2" t="s">
         <v>132</v>
       </c>
+      <c r="L28" s="15"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
+      <c r="L29" s="15"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C78440-795E-4FCC-84A9-8E0DDFC0E695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816FB190-A17D-4AB0-A1CE-2FE371E89D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
   <si>
     <t>section</t>
   </si>
@@ -581,12 +581,31 @@
     <t>Industrial Electronic Wiring Ltd</t>
   </si>
   <si>
+    <t>https://www.iew.co.uk/</t>
+  </si>
+  <si>
+    <t>Your independent family run Pet Shop. Founded in 2003 - we have 22 years of experience.
+Based in Wroughton, Swindon. Serving all surrounding villages: Marlborough, Calne, Chippenham, Stratton, Highworth, Faringdon, Lyneham, Lechlade, Wanborough....
+​2 Separate stores on the same site:
+One for Small Pets, Cage and Wild Bird, Wildlife and Reptile Foods and Accessories. We like to call this -  'littleShed'.
+One for with a huge range of Foods and Accessories for Cats and Dogs, plus Poultry and Horse items too. We like to call this -  'BIGShed'.
+Find your usual pet products at every day great prices.
+We are also fully licensed to sell Frontline and some Veterinary medicines (including foods)</t>
+  </si>
+  <si>
+    <t>/images/sponsors/petshed</t>
+  </si>
+  <si>
+    <t>Pet Shed</t>
+  </si>
+  <si>
+    <t>https://www.petshedonline.co.uk/</t>
+  </si>
+  <si>
     <t>For over 40 years, IEW Ltd. has been a cornerstone of the contract electronics manufacturing industry. With a dedicated team of over 60 professionals, we provide exemplary service to companies specialising in complex machinery.
 We are driven by a dual commitment – delivering cost-effective solutions and ensuring every assembly is delivered to time and rigorously tested, guaranteeing peak quality and reliability.
-Welcome to IEW Ltd. – Where Innovation Meets Commitment.</t>
-  </si>
-  <si>
-    <t>https://www.iew.co.uk/</t>
+Welcome to IEW Ltd.
+Where Innovation Meets Commitment.</t>
   </si>
 </sst>
 </file>
@@ -2312,7 +2331,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2347,10 +2366,10 @@
         <v>164</v>
       </c>
       <c r="L24" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="M24" t="s">
         <v>166</v>
-      </c>
-      <c r="M24" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
@@ -2413,7 +2432,7 @@
       </c>
       <c r="L26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2441,7 +2460,18 @@
       <c r="I27" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="L27" s="15"/>
+      <c r="J27" t="s">
+        <v>169</v>
+      </c>
+      <c r="K27" t="s">
+        <v>168</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="M27" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816FB190-A17D-4AB0-A1CE-2FE371E89D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7366A-0B37-4421-8CB2-ED8B86D2A0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="172">
   <si>
     <t>section</t>
   </si>
@@ -593,9 +593,6 @@
 We are also fully licensed to sell Frontline and some Veterinary medicines (including foods)</t>
   </si>
   <si>
-    <t>/images/sponsors/petshed</t>
-  </si>
-  <si>
     <t>Pet Shed</t>
   </si>
   <si>
@@ -606,6 +603,9 @@
 We are driven by a dual commitment – delivering cost-effective solutions and ensuring every assembly is delivered to time and rigorously tested, guaranteeing peak quality and reliability.
 Welcome to IEW Ltd.
 Where Innovation Meets Commitment.</t>
+  </si>
+  <si>
+    <t>/images/sponsors/petshed.png</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2366,7 @@
         <v>164</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M24" t="s">
         <v>166</v>
@@ -2460,20 +2460,11 @@
       <c r="I27" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="J27" t="s">
-        <v>169</v>
-      </c>
-      <c r="K27" t="s">
-        <v>168</v>
-      </c>
       <c r="L27" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="M27" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:13" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2501,7 +2492,18 @@
       <c r="I28" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="L28" s="15"/>
+      <c r="J28" t="s">
+        <v>168</v>
+      </c>
+      <c r="K28" t="s">
+        <v>171</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="M28" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7366A-0B37-4421-8CB2-ED8B86D2A0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E45E0-846D-4D1B-9CE4-485F408B1967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <si>
     <t>section</t>
   </si>
@@ -606,6 +606,15 @@
   </si>
   <si>
     <t>/images/sponsors/petshed.png</t>
+  </si>
+  <si>
+    <t>Your independent family run Pet Shop. Founded in 2003 - we have 22 years of experience.
+Based in Wroughton, Swindon. Serving all surrounding villages: Marlborough, Calne, Chippenham, Stratton, Highworth, Faringdon, Lyneham, Lechlade, Wanborough.
+​We have 2 Separate stores on the same site:
+One for Small Pets, Cage and Wild Bird, Wildlife and Reptile Foods and Accessories. We like to call this -  'littleShed'.
+One for with a huge range of Foods and Accessories for Cats and Dogs, plus Poultry and Horse items too. We like to call this -  'BIGShed'.
+Find your usual pet products at every day great prices.
+We are also fully licensed to sell Frontline and some Veterinary medicines (including foods)</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2508,7 @@
         <v>171</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M28" t="s">
         <v>169</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E45E0-846D-4D1B-9CE4-485F408B1967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD92DDA8-F3ED-4BB0-8E8E-C2514180FD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -609,8 +609,7 @@
   </si>
   <si>
     <t>Your independent family run Pet Shop. Founded in 2003 - we have 22 years of experience.
-Based in Wroughton, Swindon. Serving all surrounding villages: Marlborough, Calne, Chippenham, Stratton, Highworth, Faringdon, Lyneham, Lechlade, Wanborough.
-​We have 2 Separate stores on the same site:
+Based in Wroughton, Swindon. Serving all surrounding villages: Marlborough, Calne, Chippenham, Stratton, Highworth, Faringdon, Lyneham, Lechlade, Wanborough.   ​We have 2 Separate stores on the same site:
 One for Small Pets, Cage and Wild Bird, Wildlife and Reptile Foods and Accessories. We like to call this -  'littleShed'.
 One for with a huge range of Foods and Accessories for Cats and Dogs, plus Poultry and Horse items too. We like to call this -  'BIGShed'.
 Find your usual pet products at every day great prices.

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD92DDA8-F3ED-4BB0-8E8E-C2514180FD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1BB29-9A19-431A-B8B0-FAAC541ED715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,6 +50,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{B78FC473-DE6E-4838-A3E9-1CCA1A76441A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crowe:</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
@@ -79,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="175">
   <si>
     <t>section</t>
   </si>
@@ -615,12 +629,18 @@
 Find your usual pet products at every day great prices.
 We are also fully licensed to sell Frontline and some Veterinary medicines (including foods)</t>
   </si>
+  <si>
+    <t>gallery</t>
+  </si>
+  <si>
+    <t>/images/teams/magic/magic1.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,6 +838,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1577,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -1595,7 +1622,7 @@
     <col min="13" max="13" width="39.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1635,8 +1662,11 @@
       <c r="M1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="69" x14ac:dyDescent="0.3">
+      <c r="N1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1677,7 +1707,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="66.599999999999994" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1718,7 +1748,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1748,7 +1778,7 @@
       </c>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1776,8 +1806,11 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="N5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1806,7 +1839,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1835,7 +1868,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1864,7 +1897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1893,7 +1926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="55.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1934,7 +1967,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1963,7 +1996,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1992,7 +2025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -2021,7 +2054,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2050,7 +2083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -2091,7 +2124,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="285.60000000000002" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="285.60000000000002" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E1BB29-9A19-431A-B8B0-FAAC541ED715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A65BC21-BBEB-49B3-AC57-03C6621EBBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,20 +50,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{B78FC473-DE6E-4838-A3E9-1CCA1A76441A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>William Crowe:</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
@@ -640,7 +626,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,13 +824,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1620,6 +1599,7 @@
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
     <col min="12" max="12" width="84.6640625" customWidth="1"/>
     <col min="13" max="13" width="39.5546875" customWidth="1"/>
+    <col min="14" max="14" width="31.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1747,6 +1727,9 @@
       <c r="M3" s="2" t="s">
         <v>140</v>
       </c>
+      <c r="N3" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1806,9 +1789,6 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="N5" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -2124,7 +2104,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="285.60000000000002" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A65BC21-BBEB-49B3-AC57-03C6621EBBBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEA983F-88B7-4399-9C3C-CBE3D9AE60E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     <t>gallery</t>
   </si>
   <si>
-    <t>/images/teams/magic/magic1.jpg</t>
+    <t>/images/teams/magic/magic1.jpg ¦ /images/teams/magic/magic2.jpg</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEA983F-88B7-4399-9C3C-CBE3D9AE60E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB293054-8D2F-45A9-8EB7-624A7E55CCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     <t>gallery</t>
   </si>
   <si>
-    <t>/images/teams/magic/magic1.jpg ¦ /images/teams/magic/magic2.jpg</t>
+    <t>/images/teams/magic/magic1.jpg | /images/teams/magic/magic2.jpg</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB293054-8D2F-45A9-8EB7-624A7E55CCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29BD2C6-8AAD-4751-B870-AADA9882BF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -619,7 +619,7 @@
     <t>gallery</t>
   </si>
   <si>
-    <t>/images/teams/magic/magic1.jpg | /images/teams/magic/magic2.jpg</t>
+    <t>/images/teams/magic/magic1.jpg | /images/teams/magic/magic2.jpg | /images/teams/magic/magic3.jpg</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29BD2C6-8AAD-4751-B870-AADA9882BF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6499CB1-E3B9-4E54-80BE-7C2A6CD46116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,6 +50,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crowe:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
@@ -79,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="183">
   <si>
     <t>section</t>
   </si>
@@ -621,12 +645,36 @@
   <si>
     <t>/images/teams/magic/magic1.jpg | /images/teams/magic/magic2.jpg | /images/teams/magic/magic3.jpg</t>
   </si>
+  <si>
+    <t>Southby Financial Planning</t>
+  </si>
+  <si>
+    <t>/images/sponsors/southby.png</t>
+  </si>
+  <si>
+    <t>At Southby &amp; Co Financial Planning, we help and support individuals, families, and local businesses with all aspects of financial planning to ensure that their hard work is rewarded to its full potential. </t>
+  </si>
+  <si>
+    <t>https://www.southbyfp.co.uk/</t>
+  </si>
+  <si>
+    <t>Holloway Bond</t>
+  </si>
+  <si>
+    <t>/images/sponsors/holloway.png</t>
+  </si>
+  <si>
+    <t>We're a team of business rates experts, and we're confident that we can save our clients money. Operating on a no win no fee basis, with a 97% success rate, we're proud to offer a better level of service to the businesses that we work with.</t>
+  </si>
+  <si>
+    <t>https://www.hollowaybond.co.uk/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -825,6 +873,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3D4850"/>
+      <name val="Poppins"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1168,7 +1234,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1207,6 +1273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2034,7 +2101,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2061,6 +2128,18 @@
       </c>
       <c r="I14" s="2" t="s">
         <v>28</v>
+      </c>
+      <c r="J14" t="s">
+        <v>175</v>
+      </c>
+      <c r="K14" t="s">
+        <v>176</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2172,6 +2251,18 @@
       </c>
       <c r="I17" s="2" t="s">
         <v>85</v>
+      </c>
+      <c r="J17" t="s">
+        <v>179</v>
+      </c>
+      <c r="K17" t="s">
+        <v>180</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="M17" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
@@ -2687,10 +2778,11 @@
     <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
     <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
     <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
+    <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId27"/>
-  <legacyDrawing r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId28"/>
+  <legacyDrawing r:id="rId29"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6499CB1-E3B9-4E54-80BE-7C2A6CD46116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F214D73-177D-462D-8BE6-02489436EA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -649,9 +649,6 @@
     <t>Southby Financial Planning</t>
   </si>
   <si>
-    <t>/images/sponsors/southby.png</t>
-  </si>
-  <si>
     <t>At Southby &amp; Co Financial Planning, we help and support individuals, families, and local businesses with all aspects of financial planning to ensure that their hard work is rewarded to its full potential. </t>
   </si>
   <si>
@@ -668,6 +665,9 @@
   </si>
   <si>
     <t>https://www.hollowaybond.co.uk/</t>
+  </si>
+  <si>
+    <t>/images/sponsors/davesouthby.jpg</t>
   </si>
 </sst>
 </file>
@@ -2133,13 +2133,13 @@
         <v>175</v>
       </c>
       <c r="K14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2253,16 +2253,16 @@
         <v>85</v>
       </c>
       <c r="J17" t="s">
+        <v>178</v>
+      </c>
+      <c r="K17" t="s">
         <v>179</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" t="s">
         <v>181</v>
-      </c>
-      <c r="M17" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F214D73-177D-462D-8BE6-02489436EA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2E7743-47A7-4125-AD53-6260C07273D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="184">
   <si>
     <t>section</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>/images/sponsors/davesouthby.jpg</t>
+  </si>
+  <si>
+    <t>/images/sponsors/wasps.webp</t>
   </si>
 </sst>
 </file>
@@ -2401,6 +2404,9 @@
       <c r="I22" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="K22" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="23" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2E7743-47A7-4125-AD53-6260C07273D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A579B9CB-A67B-4DD7-991E-1617506DEAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="184">
   <si>
     <t>section</t>
   </si>
@@ -2404,6 +2404,9 @@
       <c r="I22" s="2" t="s">
         <v>104</v>
       </c>
+      <c r="J22" t="s">
+        <v>102</v>
+      </c>
       <c r="K22" t="s">
         <v>183</v>
       </c>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A579B9CB-A67B-4DD7-991E-1617506DEAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57896811-9D8B-437F-9B55-816B920E2A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="185">
   <si>
     <t>section</t>
   </si>
@@ -671,6 +671,9 @@
   </si>
   <si>
     <t>/images/sponsors/wasps.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/blackcats/blackcats2.jpg |  /images/teams/blackcats/blackcats.jpg</t>
   </si>
 </sst>
 </file>
@@ -1756,6 +1759,9 @@
       <c r="M2" t="s">
         <v>148</v>
       </c>
+      <c r="N2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A3" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57896811-9D8B-437F-9B55-816B920E2A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC02691-EFCB-40B2-9817-BAE2AD453D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="186">
   <si>
     <t>section</t>
   </si>
@@ -674,6 +674,9 @@
   </si>
   <si>
     <t>/images/teams/blackcats/blackcats2.jpg |  /images/teams/blackcats/blackcats.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/dragons/dragons1/webp | /images/teams/dragons/dragons2.webp | /images/teams/dragons/dragons3.webp</t>
   </si>
 </sst>
 </file>
@@ -1981,6 +1984,9 @@
       <c r="I9" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="N9" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC02691-EFCB-40B2-9817-BAE2AD453D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C399E468-7DAB-4F96-A864-A7232FB8A964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="187">
   <si>
     <t>section</t>
   </si>
@@ -676,7 +676,10 @@
     <t>/images/teams/blackcats/blackcats2.jpg |  /images/teams/blackcats/blackcats.jpg</t>
   </si>
   <si>
-    <t>/images/teams/dragons/dragons1/webp | /images/teams/dragons/dragons2.webp | /images/teams/dragons/dragons3.webp</t>
+    <t>/images/teams/dragons/dragons1.webp | /images/teams/dragons/dragons2.webp | /images/teams/dragons/dragons3.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/hurricanes/hurricanes.webp | /images/teams/hurricanes/hurricanes2.webp | /images/teams/hurricanes/hurricanes3.jpg</t>
   </si>
 </sst>
 </file>
@@ -2239,7 +2242,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2280,7 +2283,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -2307,7 +2310,7 @@
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2359,7 +2362,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2388,7 +2391,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2423,7 +2426,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2464,7 +2467,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2504,8 +2507,11 @@
       <c r="M24" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="N24" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2535,7 +2541,7 @@
       </c>
       <c r="L25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2565,7 +2571,7 @@
       </c>
       <c r="L26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2597,7 +2603,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2638,17 +2644,17 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C399E468-7DAB-4F96-A864-A7232FB8A964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50607B92-C9B3-4B60-8C9C-34BF5E8FBA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="188">
   <si>
     <t>section</t>
   </si>
@@ -679,7 +679,10 @@
     <t>/images/teams/dragons/dragons1.webp | /images/teams/dragons/dragons2.webp | /images/teams/dragons/dragons3.webp</t>
   </si>
   <si>
-    <t>/images/teams/hurricanes/hurricanes.webp | /images/teams/hurricanes/hurricanes2.webp | /images/teams/hurricanes/hurricanes3.jpg</t>
+    <t>/images/teams/hurricanes/hurricanes.webp | /images/teams/hurricanes/hurricanes2.jpg | /images/teams/hurricanes/hurricanes3.jpg</t>
+  </si>
+  <si>
+    <t>/images/team/lightning/lightening.jpg | /images/team/lightning/lightening.webp</t>
   </si>
 </sst>
 </file>
@@ -2031,6 +2034,9 @@
       <c r="M10" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="N10" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50607B92-C9B3-4B60-8C9C-34BF5E8FBA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6277509C-3189-4EEC-BE8E-4969330DD1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -682,7 +682,7 @@
     <t>/images/teams/hurricanes/hurricanes.webp | /images/teams/hurricanes/hurricanes2.jpg | /images/teams/hurricanes/hurricanes3.jpg</t>
   </si>
   <si>
-    <t>/images/team/lightning/lightening.jpg | /images/team/lightning/lightening.webp</t>
+    <t>/images/teams/lightning/lightning.jpg | /images/teams/lightning/lightning.webp</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6277509C-3189-4EEC-BE8E-4969330DD1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030B2B7C-235D-4D21-B5B4-261BFDA86F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="189">
   <si>
     <t>section</t>
   </si>
@@ -683,6 +683,9 @@
   </si>
   <si>
     <t>/images/teams/lightning/lightning.jpg | /images/teams/lightning/lightning.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens.webp | /images/teams/wrens/wresn3.jpg</t>
   </si>
 </sst>
 </file>
@@ -2247,6 +2250,9 @@
       <c r="M16" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="N16" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030B2B7C-235D-4D21-B5B4-261BFDA86F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7DD435-CC02-48ED-B31B-11ECFDDB7CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="192">
   <si>
     <t>section</t>
   </si>
@@ -686,6 +686,15 @@
   </si>
   <si>
     <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens.webp | /images/teams/wrens/wresn3.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/warriors/warriors.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/ravens/ravens.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/wookies/wookies.jpg | /images/teams/wookies/wookies2.jpg</t>
   </si>
 </sst>
 </file>
@@ -2127,6 +2136,9 @@
       <c r="I13" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="N13" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
@@ -2168,6 +2180,9 @@
       <c r="M14" s="2" t="s">
         <v>177</v>
       </c>
+      <c r="N14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -2293,6 +2308,9 @@
       </c>
       <c r="M17" t="s">
         <v>181</v>
+      </c>
+      <c r="N17" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7DD435-CC02-48ED-B31B-11ECFDDB7CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0577409F-485F-4903-9AA2-885D8291BE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -47,6 +47,44 @@
           </rPr>
           <t xml:space="preserve">
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crowe:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+ag</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Cro</t>
         </r>
       </text>
     </comment>
@@ -103,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="198">
   <si>
     <t>section</t>
   </si>
@@ -685,9 +723,6 @@
     <t>/images/teams/lightning/lightning.jpg | /images/teams/lightning/lightning.webp</t>
   </si>
   <si>
-    <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens.webp | /images/teams/wrens/wresn3.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/warriors/warriors.jpg</t>
   </si>
   <si>
@@ -695,6 +730,27 @@
   </si>
   <si>
     <t>/images/teams/wookies/wookies.jpg | /images/teams/wookies/wookies2.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens3.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/rangers/rangers.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/wolves/wolves.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/rams/rams.webp</t>
+  </si>
+  <si>
+    <t>/images/teams/rhinos/rhinos.jpg | /images/teams/rhinos/rhinos2.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/panhers/panthers.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/foxes/foxes.webp</t>
   </si>
 </sst>
 </file>
@@ -1857,6 +1913,9 @@
         <v>32</v>
       </c>
       <c r="L4" s="10"/>
+      <c r="N4" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1886,6 +1945,9 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
+      <c r="N5" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1915,6 +1977,9 @@
       <c r="I6" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="N6" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1944,6 +2009,9 @@
       <c r="I7" t="s">
         <v>47</v>
       </c>
+      <c r="N7" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -2078,6 +2146,9 @@
       <c r="I11" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="N11" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -2137,7 +2208,7 @@
         <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2181,7 +2252,7 @@
         <v>177</v>
       </c>
       <c r="N14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2266,7 +2337,7 @@
         <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2310,7 +2381,7 @@
         <v>181</v>
       </c>
       <c r="N17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2495,6 +2566,9 @@
       </c>
       <c r="M23" t="s">
         <v>153</v>
+      </c>
+      <c r="N23" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0577409F-485F-4903-9AA2-885D8291BE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3193C7C-092C-47E0-AE9E-038604458EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="199">
   <si>
     <t>section</t>
   </si>
@@ -741,16 +741,19 @@
     <t>/images/teams/wolves/wolves.webp</t>
   </si>
   <si>
-    <t>/images/teams/rams/rams.webp</t>
-  </si>
-  <si>
     <t>/images/teams/rhinos/rhinos.jpg | /images/teams/rhinos/rhinos2.jpg</t>
   </si>
   <si>
-    <t>/images/teams/panhers/panthers.jpg</t>
-  </si>
-  <si>
-    <t>/images/teams/foxes/foxes.webp</t>
+    <t>/images/teams/panthers/panthers.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/rams/rams.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/foxes/foxes.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/tornadoes/tornadoes.jpg</t>
   </si>
 </sst>
 </file>
@@ -1914,7 +1917,7 @@
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1946,7 +1949,7 @@
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1978,7 +1981,7 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2644,6 +2647,9 @@
         <v>119</v>
       </c>
       <c r="L25" s="15"/>
+      <c r="N25" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3193C7C-092C-47E0-AE9E-038604458EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5121448D-C6DA-4A39-B140-168490437654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -711,9 +711,6 @@
     <t>/images/sponsors/wasps.webp</t>
   </si>
   <si>
-    <t>/images/teams/blackcats/blackcats2.jpg |  /images/teams/blackcats/blackcats.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/dragons/dragons1.webp | /images/teams/dragons/dragons2.webp | /images/teams/dragons/dragons3.webp</t>
   </si>
   <si>
@@ -754,6 +751,9 @@
   </si>
   <si>
     <t>/images/teams/tornadoes/tornadoes.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/blackcats/girls.jpg |  /images/teams/blackcats/blackcats.jpg</t>
   </si>
 </sst>
 </file>
@@ -1840,7 +1840,7 @@
         <v>148</v>
       </c>
       <c r="N2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1949,7 +1949,7 @@
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -1981,7 +1981,7 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2013,7 +2013,7 @@
         <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2074,7 +2074,7 @@
         <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2118,7 +2118,7 @@
         <v>163</v>
       </c>
       <c r="N10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2150,7 +2150,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2211,7 +2211,7 @@
         <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2255,7 +2255,7 @@
         <v>177</v>
       </c>
       <c r="N14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2340,7 +2340,7 @@
         <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2384,7 +2384,7 @@
         <v>181</v>
       </c>
       <c r="N17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2571,7 +2571,7 @@
         <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2615,7 +2615,7 @@
         <v>166</v>
       </c>
       <c r="N24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5121448D-C6DA-4A39-B140-168490437654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C78D58-E603-44B4-BDA1-278911666157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -753,7 +753,7 @@
     <t>/images/teams/tornadoes/tornadoes.jpg</t>
   </si>
   <si>
-    <t>/images/teams/blackcats/girls.jpg |  /images/teams/blackcats/blackcats.jpg</t>
+    <t>/images/teams/blackcats/blackcats4.jpg |  /images/teams/blackcats/blackcats.jpg |  /images/teams/blackcats/blackcats5.jpg</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C78D58-E603-44B4-BDA1-278911666157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C702E6-2C19-4237-949B-F9E08932A496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -136,12 +136,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>William Crow</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="201">
   <si>
     <t>section</t>
   </si>
@@ -754,6 +768,12 @@
   </si>
   <si>
     <t>/images/teams/blackcats/blackcats4.jpg |  /images/teams/blackcats/blackcats.jpg |  /images/teams/blackcats/blackcats5.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/mens/mens.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/u18/u18.jpg</t>
   </si>
 </sst>
 </file>
@@ -2413,6 +2433,9 @@
         <v>90</v>
       </c>
       <c r="L18" s="12"/>
+      <c r="N18" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -2752,6 +2775,9 @@
       </c>
       <c r="M28" t="s">
         <v>169</v>
+      </c>
+      <c r="N28" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C702E6-2C19-4237-949B-F9E08932A496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5B441E-270C-4815-9686-F093AEAB5E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -88,6 +88,9 @@
         </r>
       </text>
     </comment>
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
+      <text/>
+    </comment>
     <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
       <text>
         <r>
@@ -155,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="202">
   <si>
     <t>section</t>
   </si>
@@ -774,6 +777,9 @@
   </si>
   <si>
     <t>/images/teams/u18/u18.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/thunder.jpg</t>
   </si>
 </sst>
 </file>
@@ -2201,6 +2207,9 @@
       <c r="I12" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="N12" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5B441E-270C-4815-9686-F093AEAB5E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16381A45-32D3-4228-8A88-4BECBBA2B27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -779,7 +779,7 @@
     <t>/images/teams/u18/u18.jpg</t>
   </si>
   <si>
-    <t>/images/teams/thunder.jpg</t>
+    <t>/images/teams/thunder/thunder.jpg</t>
   </si>
 </sst>
 </file>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16381A45-32D3-4228-8A88-4BECBBA2B27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020176A8-833D-401D-976C-9F476EB116D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -153,12 +153,15 @@
         </r>
       </text>
     </comment>
+    <comment ref="N22" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
+      <text/>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="203">
   <si>
     <t>section</t>
   </si>
@@ -780,6 +783,9 @@
   </si>
   <si>
     <t>/images/teams/thunder/thunder.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/wasps/wasps1.jpg</t>
   </si>
 </sst>
 </file>
@@ -2561,6 +2567,9 @@
       <c r="K22" t="s">
         <v>183</v>
       </c>
+      <c r="N22" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020176A8-833D-401D-976C-9F476EB116D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6366F-F453-4C13-858D-BDA4C25D4F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -749,15 +749,9 @@
     <t>/images/teams/wookies/wookies.jpg | /images/teams/wookies/wookies2.jpg</t>
   </si>
   <si>
-    <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens3.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/rangers/rangers.webp</t>
   </si>
   <si>
-    <t>/images/teams/wolves/wolves.webp</t>
-  </si>
-  <si>
     <t>/images/teams/rhinos/rhinos.jpg | /images/teams/rhinos/rhinos2.jpg</t>
   </si>
   <si>
@@ -767,9 +761,6 @@
     <t>/images/teams/rams/rams.jpg</t>
   </si>
   <si>
-    <t>/images/teams/foxes/foxes.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/tornadoes/tornadoes.jpg</t>
   </si>
   <si>
@@ -786,6 +777,15 @@
   </si>
   <si>
     <t>/images/teams/wasps/wasps1.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/foxes/foxes.jpg | /inages/teams/foxes/foxes1.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens3.jpg | /images/teams/wrens/wrens4.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/wolves/wolves.webp | /images/teams/wolves/wolves.jpg</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1872,7 @@
         <v>148</v>
       </c>
       <c r="N2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1981,7 +1981,7 @@
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2013,7 +2013,7 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2045,7 +2045,7 @@
         <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2182,7 +2182,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2214,7 +2214,7 @@
         <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2375,7 +2375,7 @@
         <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2568,7 +2568,7 @@
         <v>183</v>
       </c>
       <c r="N22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2612,7 +2612,7 @@
         <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2795,7 +2795,7 @@
         <v>169</v>
       </c>
       <c r="N28" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6366F-F453-4C13-858D-BDA4C25D4F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F773A5A-F25E-4FC6-9226-1A11F5B5D6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -779,13 +779,13 @@
     <t>/images/teams/wasps/wasps1.jpg</t>
   </si>
   <si>
-    <t>/images/teams/foxes/foxes.jpg | /inages/teams/foxes/foxes1.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/wrens/wrens.jpg | /images/teams/wrens/wrens3.jpg | /images/teams/wrens/wrens4.jpg</t>
   </si>
   <si>
     <t>/images/teams/wolves/wolves.webp | /images/teams/wolves/wolves.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/foxes/foxes.jpg | /images/teams/foxes/foxes1.jpg</t>
   </si>
 </sst>
 </file>
@@ -2182,7 +2182,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2375,7 +2375,7 @@
         <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2612,7 +2612,7 @@
         <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F773A5A-F25E-4FC6-9226-1A11F5B5D6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26D93C-3935-4CA2-971E-F20ED82C04B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -749,18 +749,12 @@
     <t>/images/teams/wookies/wookies.jpg | /images/teams/wookies/wookies2.jpg</t>
   </si>
   <si>
-    <t>/images/teams/rangers/rangers.webp</t>
-  </si>
-  <si>
     <t>/images/teams/rhinos/rhinos.jpg | /images/teams/rhinos/rhinos2.jpg</t>
   </si>
   <si>
     <t>/images/teams/panthers/panthers.jpg</t>
   </si>
   <si>
-    <t>/images/teams/rams/rams.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/tornadoes/tornadoes.jpg</t>
   </si>
   <si>
@@ -773,9 +767,6 @@
     <t>/images/teams/u18/u18.jpg</t>
   </si>
   <si>
-    <t>/images/teams/thunder/thunder.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/wasps/wasps1.jpg</t>
   </si>
   <si>
@@ -786,6 +777,15 @@
   </si>
   <si>
     <t>/images/teams/foxes/foxes.jpg | /images/teams/foxes/foxes1.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/rams/rams.jpg | /images/teams/rams/rrt.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/rangers/rangers.webp | /images/teams/rams/rrt.jpg</t>
+  </si>
+  <si>
+    <t>/images/teams/thunder/thunder.jpg | /images/teams/rams/rrt.jpg</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1872,7 @@
         <v>148</v>
       </c>
       <c r="N2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1981,7 +1981,7 @@
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2013,7 +2013,7 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2045,7 +2045,7 @@
         <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2182,7 +2182,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2214,7 +2214,7 @@
         <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2375,7 +2375,7 @@
         <v>153</v>
       </c>
       <c r="N16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2568,7 +2568,7 @@
         <v>183</v>
       </c>
       <c r="N22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2612,7 +2612,7 @@
         <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2795,7 +2795,7 @@
         <v>169</v>
       </c>
       <c r="N28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA26D93C-3935-4CA2-971E-F20ED82C04B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025ACF81-A87C-4C78-BCB8-614DE05CAFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -436,9 +436,6 @@
     <t>wyfc.chair@gmail.com</t>
   </si>
   <si>
-    <t>Ability-Counts</t>
-  </si>
-  <si>
     <t>tbc</t>
   </si>
   <si>
@@ -786,6 +783,9 @@
   </si>
   <si>
     <t>/images/teams/thunder/thunder.jpg | /images/teams/rams/rrt.jpg</t>
+  </si>
+  <si>
+    <t>Jaguars (Ability Counts)</t>
   </si>
 </sst>
 </file>
@@ -1816,19 +1816,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" t="s">
         <v>137</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>138</v>
       </c>
-      <c r="L1" t="s">
-        <v>139</v>
-      </c>
       <c r="M1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
@@ -1854,25 +1854,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
         <v>41</v>
       </c>
       <c r="J2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K2" t="s">
         <v>146</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="M2" t="s">
         <v>147</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="M2" t="s">
-        <v>148</v>
-      </c>
       <c r="N2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1889,7 +1889,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1898,25 +1898,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -1942,14 +1942,14 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1975,13 +1975,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2007,13 +2007,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2045,7 +2045,7 @@
         <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2071,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>51</v>
@@ -2106,7 +2106,7 @@
         <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2138,19 +2138,19 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K10" t="s">
+        <v>159</v>
+      </c>
+      <c r="L10" t="s">
         <v>161</v>
       </c>
-      <c r="K10" t="s">
-        <v>160</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="N10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2182,7 +2182,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2214,7 +2214,7 @@
         <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2246,7 +2246,7 @@
         <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2278,19 +2278,19 @@
         <v>28</v>
       </c>
       <c r="J14" t="s">
+        <v>174</v>
+      </c>
+      <c r="K14" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="K14" t="s">
-        <v>182</v>
-      </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="N14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2322,16 +2322,16 @@
         <v>72</v>
       </c>
       <c r="J15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K15" t="s">
+        <v>158</v>
+      </c>
+      <c r="L15" t="s">
         <v>156</v>
       </c>
-      <c r="K15" t="s">
-        <v>159</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
@@ -2363,19 +2363,19 @@
         <v>75</v>
       </c>
       <c r="J16" t="s">
+        <v>150</v>
+      </c>
+      <c r="K16" t="s">
         <v>151</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="N16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2407,19 +2407,19 @@
         <v>85</v>
       </c>
       <c r="J17" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" t="s">
         <v>178</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" t="s">
         <v>180</v>
       </c>
-      <c r="M17" t="s">
-        <v>181</v>
-      </c>
       <c r="N17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2457,13 +2457,13 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -2472,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>90</v>
@@ -2483,13 +2483,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -2498,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
@@ -2512,13 +2512,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
         <v>97</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -2527,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2541,13 +2541,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2556,19 +2556,19 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2579,13 +2579,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
         <v>105</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2594,25 +2594,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J23" t="s">
+        <v>150</v>
+      </c>
+      <c r="K23" t="s">
         <v>151</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" t="s">
         <v>152</v>
       </c>
-      <c r="L23" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="M23" t="s">
-        <v>153</v>
-      </c>
       <c r="N23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2623,13 +2623,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" t="s">
         <v>111</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2638,25 +2638,25 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="J24" t="s">
+        <v>164</v>
+      </c>
+      <c r="K24" t="s">
+        <v>163</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M24" t="s">
         <v>165</v>
       </c>
-      <c r="K24" t="s">
-        <v>164</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="M24" t="s">
-        <v>166</v>
-      </c>
       <c r="N24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2667,13 +2667,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2682,14 +2682,14 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2700,13 +2700,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" t="s">
         <v>120</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -2715,10 +2715,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="L26" s="15"/>
     </row>
@@ -2730,13 +2730,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
         <v>125</v>
       </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -2745,13 +2745,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="L27" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2762,13 +2762,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
         <v>129</v>
       </c>
-      <c r="D28" t="s">
-        <v>130</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -2777,25 +2777,25 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="J28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" t="s">
+        <v>170</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="M28" t="s">
         <v>168</v>
       </c>
-      <c r="K28" t="s">
-        <v>171</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="M28" t="s">
-        <v>169</v>
-      </c>
       <c r="N28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025ACF81-A87C-4C78-BCB8-614DE05CAFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632A7E4E-7E22-41C5-994A-EA333062EC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="207">
   <si>
     <t>section</t>
   </si>
@@ -787,12 +787,24 @@
   <si>
     <t>Jaguars (Ability Counts)</t>
   </si>
+  <si>
+    <t>/images/sponsors/wcats.png</t>
+  </si>
+  <si>
+    <t>Wilts FA Wildcats</t>
+  </si>
+  <si>
+    <t>So, what is Wildcats? Well, it’s non-competitive football for girls who want to give it a go for the very first time or want to play with other girls their own age. Most importantly, Wildcats is all about having loads of fun and meeting new amazing friends.</t>
+  </si>
+  <si>
+    <t>https://www.englandfootball.com/play/youth-football/wildcats#:~:text=So%2C%20what%20is%20Wildcats%3F%20Well%2C,and%20meeting%20new%20amazing%20friends.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,6 +1020,12 @@
       <sz val="10"/>
       <color rgb="FF3D4850"/>
       <name val="Poppins"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF011E41"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1352,7 +1370,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1392,6 +1410,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2503,6 +2522,18 @@
       <c r="I20" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="J20" t="s">
+        <v>204</v>
+      </c>
+      <c r="K20" t="s">
+        <v>203</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -2960,10 +2991,11 @@
     <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
     <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
     <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
+    <hyperlink ref="M20" r:id="rId28" location=":~:text=So%2C%20what%20is%20Wildcats%3F%20Well%2C,and%20meeting%20new%20amazing%20friends." xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId28"/>
-  <legacyDrawing r:id="rId29"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId29"/>
+  <legacyDrawing r:id="rId30"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -2971,25 +3003,25 @@
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>F18:F1048576 I7 F1:F5 F6:F16</xm:sqref>
+          <xm:sqref>F18:F1048576 I7 F1:F16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>
             <xm:f>data!$C$1:$C$7</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A5 A6:A1048576</xm:sqref>
+          <xm:sqref>A1:A1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3A402E24-C34D-416E-85F6-ACAE2E15BCE1}">
           <x14:formula1>
             <xm:f>data!$E$2:$E$33</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B5 B6:B1048576</xm:sqref>
+          <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B8CC80F3-8A5F-4A97-9C2A-582813DC8A38}">
           <x14:formula1>
             <xm:f>data!$G$1:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G1:G5 G6:G1048576</xm:sqref>
+          <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632A7E4E-7E22-41C5-994A-EA333062EC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F712777-4121-4128-8485-136EE2701747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -785,9 +785,6 @@
     <t>/images/teams/thunder/thunder.jpg | /images/teams/rams/rrt.jpg</t>
   </si>
   <si>
-    <t>Jaguars (Ability Counts)</t>
-  </si>
-  <si>
     <t>/images/sponsors/wcats.png</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>https://www.englandfootball.com/play/youth-football/wildcats#:~:text=So%2C%20what%20is%20Wildcats%3F%20Well%2C,and%20meeting%20new%20amazing%20friends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaguars </t>
   </si>
 </sst>
 </file>
@@ -2476,7 +2476,7 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
@@ -2523,16 +2523,16 @@
         <v>13</v>
       </c>
       <c r="J20" t="s">
+        <v>203</v>
+      </c>
+      <c r="K20" t="s">
+        <v>202</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="K20" t="s">
-        <v>203</v>
-      </c>
-      <c r="L20" s="17" t="s">
+      <c r="M20" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F712777-4121-4128-8485-136EE2701747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BB28A2-A8B6-4CB8-8D6E-1426FFAE450B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -439,9 +439,6 @@
     <t>tbc</t>
   </si>
   <si>
-    <t>an exciting new Ability-Counts team - Established May 2026</t>
-  </si>
-  <si>
     <t>Wildcats</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jaguars </t>
+  </si>
+  <si>
+    <t>An exciting new Ability-Counts team - Established May 2026</t>
   </si>
 </sst>
 </file>
@@ -1835,19 +1835,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K1" t="s">
         <v>136</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>137</v>
       </c>
-      <c r="L1" t="s">
-        <v>138</v>
-      </c>
       <c r="M1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
@@ -1873,25 +1873,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>41</v>
       </c>
       <c r="J2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" t="s">
         <v>145</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="M2" t="s">
         <v>146</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="M2" t="s">
-        <v>147</v>
-      </c>
       <c r="N2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1908,7 +1908,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1917,25 +1917,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I3" t="s">
         <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -1961,14 +1961,14 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -1994,13 +1994,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I5" t="s">
         <v>37</v>
       </c>
       <c r="N5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2026,13 +2026,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2064,7 +2064,7 @@
         <v>47</v>
       </c>
       <c r="N7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>51</v>
@@ -2125,7 +2125,7 @@
         <v>55</v>
       </c>
       <c r="N9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2157,19 +2157,19 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" t="s">
+        <v>158</v>
+      </c>
+      <c r="L10" t="s">
         <v>160</v>
       </c>
-      <c r="K10" t="s">
-        <v>159</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="N10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2201,7 +2201,7 @@
         <v>62</v>
       </c>
       <c r="N11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2233,7 +2233,7 @@
         <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2265,7 +2265,7 @@
         <v>69</v>
       </c>
       <c r="N13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2297,19 +2297,19 @@
         <v>28</v>
       </c>
       <c r="J14" t="s">
+        <v>173</v>
+      </c>
+      <c r="K14" t="s">
+        <v>180</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="K14" t="s">
-        <v>181</v>
-      </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="N14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2341,16 +2341,16 @@
         <v>72</v>
       </c>
       <c r="J15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K15" t="s">
+        <v>157</v>
+      </c>
+      <c r="L15" t="s">
         <v>155</v>
       </c>
-      <c r="K15" t="s">
-        <v>158</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
@@ -2382,19 +2382,19 @@
         <v>75</v>
       </c>
       <c r="J16" t="s">
+        <v>149</v>
+      </c>
+      <c r="K16" t="s">
         <v>150</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="N16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2426,19 +2426,19 @@
         <v>85</v>
       </c>
       <c r="J17" t="s">
+        <v>176</v>
+      </c>
+      <c r="K17" t="s">
         <v>177</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" t="s">
         <v>179</v>
       </c>
-      <c r="M17" t="s">
-        <v>180</v>
-      </c>
       <c r="N17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2476,7 +2476,7 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>92</v>
+        <v>206</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>90</v>
@@ -2502,13 +2502,13 @@
         <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -2517,22 +2517,22 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J20" t="s">
+        <v>202</v>
+      </c>
+      <c r="K20" t="s">
+        <v>201</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="K20" t="s">
-        <v>202</v>
-      </c>
-      <c r="L20" s="17" t="s">
+      <c r="M20" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2543,13 +2543,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
         <v>96</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2572,13 +2572,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
         <v>101</v>
       </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -2587,19 +2587,19 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2610,13 +2610,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2625,25 +2625,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J23" t="s">
+        <v>149</v>
+      </c>
+      <c r="K23" t="s">
         <v>150</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" t="s">
         <v>151</v>
       </c>
-      <c r="L23" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="M23" t="s">
-        <v>152</v>
-      </c>
       <c r="N23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2654,13 +2654,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
         <v>110</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -2669,25 +2669,25 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="J24" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" t="s">
+        <v>162</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="M24" t="s">
         <v>164</v>
       </c>
-      <c r="K24" t="s">
-        <v>163</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="M24" t="s">
-        <v>165</v>
-      </c>
       <c r="N24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2698,13 +2698,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" t="s">
         <v>115</v>
       </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -2713,14 +2713,14 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2731,13 +2731,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
         <v>119</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -2746,10 +2746,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="L26" s="15"/>
     </row>
@@ -2761,13 +2761,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" t="s">
         <v>124</v>
       </c>
-      <c r="D27" t="s">
-        <v>125</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -2776,13 +2776,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="L27" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2793,13 +2793,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" t="s">
         <v>128</v>
       </c>
-      <c r="D28" t="s">
-        <v>129</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -2808,25 +2808,25 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="J28" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28" t="s">
+        <v>169</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="M28" t="s">
         <v>167</v>
       </c>
-      <c r="K28" t="s">
-        <v>170</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="M28" t="s">
-        <v>168</v>
-      </c>
       <c r="N28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BB28A2-A8B6-4CB8-8D6E-1426FFAE450B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D60F01-A683-4444-9F87-1554A25D7B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -791,13 +791,13 @@
     <t>So, what is Wildcats? Well, it’s non-competitive football for girls who want to give it a go for the very first time or want to play with other girls their own age. Most importantly, Wildcats is all about having loads of fun and meeting new amazing friends.</t>
   </si>
   <si>
-    <t>https://www.englandfootball.com/play/youth-football/wildcats#:~:text=So%2C%20what%20is%20Wildcats%3F%20Well%2C,and%20meeting%20new%20amazing%20friends.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jaguars </t>
   </si>
   <si>
     <t>An exciting new Ability-Counts team - Established May 2026</t>
+  </si>
+  <si>
+    <t>https://book.englandfootball.com/Wildcats/wroughtonyouthfc0/Summary/0135fcc0-f19f-471b-b3ea-ee4b060728d4</t>
   </si>
 </sst>
 </file>
@@ -2476,7 +2476,7 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>90</v>
@@ -2532,7 +2532,7 @@
         <v>203</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2991,7 +2991,7 @@
     <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
     <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
     <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
-    <hyperlink ref="M20" r:id="rId28" location=":~:text=So%2C%20what%20is%20Wildcats%3F%20Well%2C,and%20meeting%20new%20amazing%20friends." xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
+    <hyperlink ref="M20" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId29"/>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D60F01-A683-4444-9F87-1554A25D7B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586EE271-D658-442A-8618-16337FB4102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -196,9 +196,6 @@
     <t>Magic</t>
   </si>
   <si>
-    <t>Will Crowe</t>
-  </si>
-  <si>
     <t>The Deanery School</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>https://book.englandfootball.com/Wildcats/wroughtonyouthfc0/Summary/0135fcc0-f19f-471b-b3ea-ee4b060728d4</t>
+  </si>
+  <si>
+    <t>Will Crowe / Kyle J &amp; Alex King</t>
   </si>
 </sst>
 </file>
@@ -1835,19 +1835,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" t="s">
         <v>135</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>136</v>
       </c>
-      <c r="L1" t="s">
-        <v>137</v>
-      </c>
       <c r="M1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
@@ -1858,40 +1858,40 @@
         <v>2018</v>
       </c>
       <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
         <v>143</v>
       </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>144</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M2" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="M2" t="s">
-        <v>146</v>
-      </c>
       <c r="N2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1905,411 +1905,411 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>2017</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5">
         <v>2017</v>
       </c>
       <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>2016</v>
       </c>
       <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>2016</v>
       </c>
       <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>2015</v>
       </c>
       <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <v>2014</v>
       </c>
       <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
-        <v>54</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>2014</v>
       </c>
       <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="J10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K10" t="s">
+        <v>157</v>
+      </c>
+      <c r="L10" t="s">
         <v>159</v>
       </c>
-      <c r="K10" t="s">
-        <v>158</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="N10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>2014</v>
       </c>
       <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>2013</v>
       </c>
       <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>2013</v>
       </c>
       <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
       </c>
       <c r="E14" s="1">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
+        <v>172</v>
+      </c>
+      <c r="K14" t="s">
+        <v>179</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="K14" t="s">
-        <v>180</v>
-      </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="N14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2320,37 +2320,37 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
         <v>70</v>
       </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s">
+        <v>153</v>
+      </c>
+      <c r="K15" t="s">
+        <v>156</v>
+      </c>
+      <c r="L15" t="s">
         <v>154</v>
       </c>
-      <c r="K15" t="s">
-        <v>157</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
@@ -2361,40 +2361,40 @@
         <v>2010</v>
       </c>
       <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
-        <v>74</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J16" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" t="s">
         <v>149</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="N16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2405,428 +2405,428 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
         <v>76</v>
       </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J17" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" t="s">
         <v>176</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" t="s">
         <v>178</v>
       </c>
-      <c r="M17" t="s">
-        <v>179</v>
-      </c>
       <c r="N17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
         <v>86</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J20" t="s">
+        <v>201</v>
+      </c>
+      <c r="K20" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="K20" t="s">
-        <v>201</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>203</v>
-      </c>
       <c r="M20" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
         <v>95</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
         <v>103</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J23" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" t="s">
         <v>149</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="M23" t="s">
         <v>150</v>
       </c>
-      <c r="L23" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="M23" t="s">
-        <v>151</v>
-      </c>
       <c r="N23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24">
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
         <v>109</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="J24" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" t="s">
+        <v>161</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="M24" t="s">
         <v>163</v>
       </c>
-      <c r="K24" t="s">
-        <v>162</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="M24" t="s">
-        <v>164</v>
-      </c>
       <c r="N24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>2011</v>
       </c>
       <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
         <v>114</v>
       </c>
-      <c r="D25" t="s">
-        <v>115</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26">
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
         <v>118</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="L26" s="15"/>
     </row>
     <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27">
         <v>2009</v>
       </c>
       <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" t="s">
         <v>123</v>
       </c>
-      <c r="D27" t="s">
-        <v>124</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="L27" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28">
         <v>2007</v>
       </c>
       <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
         <v>127</v>
       </c>
-      <c r="D28" t="s">
-        <v>128</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="J28" t="s">
+        <v>165</v>
+      </c>
+      <c r="K28" t="s">
+        <v>168</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M28" t="s">
         <v>166</v>
       </c>
-      <c r="K28" t="s">
-        <v>169</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="M28" t="s">
-        <v>167</v>
-      </c>
       <c r="N28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -3054,10 +3054,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>2000</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>2001</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>2003</v>
@@ -3104,10 +3104,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>2004</v>
@@ -3115,10 +3115,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>2005</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8">
         <v>2006</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>2007</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586EE271-D658-442A-8618-16337FB4102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8CB8FC-3FB5-47BA-A1B6-B775EF79FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -91,6 +91,9 @@
     <comment ref="N12" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
       <text/>
     </comment>
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
+      <text/>
+    </comment>
     <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
       <text>
         <r>
@@ -161,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="211">
   <si>
     <t>section</t>
   </si>
@@ -798,6 +801,19 @@
   </si>
   <si>
     <t>Will Crowe / Kyle J &amp; Alex King</t>
+  </si>
+  <si>
+    <t>Jam Interiors Ltd</t>
+  </si>
+  <si>
+    <t>/images/sponsors/jam.jpg</t>
+  </si>
+  <si>
+    <t>When we founded JAM Interiors in 2006, our plan was to create a family-run company that specialises in excellence and perfect interior design.
+Our ethos hasn’t changed. Our task is still to deliver the highest level of design, practicality and service. We’re proud of our reputation for getting it right, the first time, every time.</t>
+  </si>
+  <si>
+    <t>https://jaminteriorsgroup.com/</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1386,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1411,6 +1427,9 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2236,7 +2255,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2263,6 +2282,18 @@
       </c>
       <c r="I13" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="J13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="M13" t="s">
+        <v>210</v>
       </c>
       <c r="N13" t="s">
         <v>186</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8CB8FC-3FB5-47BA-A1B6-B775EF79FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71911724-CBFA-41E5-85B7-21322C2EF582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="210">
   <si>
     <t>section</t>
   </si>
@@ -809,11 +809,7 @@
     <t>/images/sponsors/jam.jpg</t>
   </si>
   <si>
-    <t>When we founded JAM Interiors in 2006, our plan was to create a family-run company that specialises in excellence and perfect interior design.
-Our ethos hasn’t changed. Our task is still to deliver the highest level of design, practicality and service. We’re proud of our reputation for getting it right, the first time, every time.</t>
-  </si>
-  <si>
-    <t>https://jaminteriorsgroup.com/</t>
+    <t>JAM Interiors Limited specialises in Drylining, Plastering, buildng partition walls and ceilings &amp; metsec projects.</t>
   </si>
 </sst>
 </file>
@@ -2255,7 +2251,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2291,9 +2287,6 @@
       </c>
       <c r="L13" s="18" t="s">
         <v>209</v>
-      </c>
-      <c r="M13" t="s">
-        <v>210</v>
       </c>
       <c r="N13" t="s">
         <v>186</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71911724-CBFA-41E5-85B7-21322C2EF582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF029F60-BEA6-468A-B408-5CE9F5203ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -73,6 +73,9 @@
 ag</t>
         </r>
       </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
+      <text/>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
       <text>
@@ -164,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="214">
   <si>
     <t>section</t>
   </si>
@@ -810,6 +813,20 @@
   </si>
   <si>
     <t>JAM Interiors Limited specialises in Drylining, Plastering, buildng partition walls and ceilings &amp; metsec projects.</t>
+  </si>
+  <si>
+    <t>The Fox &amp; Hounds</t>
+  </si>
+  <si>
+    <t>/images/sponsors/fox.jpg</t>
+  </si>
+  <si>
+    <t>With many years experience in the hospitality trade, Paul, James &amp; The Team pride themselves on the Friendly &amp; Professional service they offer in a relaxed &amp; inviting environment. 
+The Fox &amp; Hounds at Wroughton offers a smart, cool interior, an excellent menu and a plentiful range of food and drink.
+We're nestled into the hillside a short walk from Wroughton high street in the beautiful Wiltshire countryside on the outskirts of Swindon, just 10 mins drive from Jct 15 of the M4.</t>
+  </si>
+  <si>
+    <t>https://www.thefoxwroughton.com/</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +2204,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2214,6 +2231,18 @@
       </c>
       <c r="I11" s="3" t="s">
         <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>210</v>
+      </c>
+      <c r="K11" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="N11" t="s">
         <v>196</v>
@@ -3016,10 +3045,11 @@
     <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
     <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
     <hyperlink ref="M20" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
+    <hyperlink ref="M11" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId29"/>
-  <legacyDrawing r:id="rId30"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId30"/>
+  <legacyDrawing r:id="rId31"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF029F60-BEA6-468A-B408-5CE9F5203ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9682F3-0A36-4F72-A35A-59DCC6F03FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -349,9 +349,6 @@
     <t>Foxes</t>
   </si>
   <si>
-    <t xml:space="preserve">Mehdi </t>
-  </si>
-  <si>
     <t>wyfc.foxes@gmail.com</t>
   </si>
   <si>
@@ -827,6 +824,9 @@
   </si>
   <si>
     <t>https://www.thefoxwroughton.com/</t>
+  </si>
+  <si>
+    <t>Mehdi  Najafi / Richie Lester</t>
   </si>
 </sst>
 </file>
@@ -1867,19 +1867,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
         <v>134</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>135</v>
       </c>
-      <c r="L1" t="s">
-        <v>136</v>
-      </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
@@ -1905,25 +1905,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
       </c>
       <c r="J2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" t="s">
         <v>143</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="M2" t="s">
         <v>144</v>
       </c>
-      <c r="L2" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="M2" t="s">
-        <v>145</v>
-      </c>
       <c r="N2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1937,10 +1937,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1949,25 +1949,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -1993,14 +1993,14 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -2026,13 +2026,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I5" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2058,13 +2058,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2090,13 +2090,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I7" t="s">
         <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>50</v>
@@ -2151,13 +2151,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2189,19 +2189,19 @@
         <v>58</v>
       </c>
       <c r="J10" t="s">
+        <v>157</v>
+      </c>
+      <c r="K10" t="s">
+        <v>156</v>
+      </c>
+      <c r="L10" t="s">
         <v>158</v>
       </c>
-      <c r="K10" t="s">
-        <v>157</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M10" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="N10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
@@ -2215,7 +2215,7 @@
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2227,25 +2227,25 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J11" t="s">
+        <v>209</v>
+      </c>
+      <c r="K11" t="s">
         <v>210</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="M11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="N11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2256,10 +2256,10 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2271,13 +2271,13 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2288,10 +2288,10 @@
         <v>2013</v>
       </c>
       <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
         <v>66</v>
-      </c>
-      <c r="D13" t="s">
-        <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2303,22 +2303,22 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K13" t="s">
         <v>207</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="L13" s="18" t="s">
-        <v>209</v>
-      </c>
       <c r="N13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2350,19 +2350,19 @@
         <v>27</v>
       </c>
       <c r="J14" t="s">
+        <v>171</v>
+      </c>
+      <c r="K14" t="s">
+        <v>178</v>
+      </c>
+      <c r="L14" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="K14" t="s">
-        <v>179</v>
-      </c>
-      <c r="L14" s="16" t="s">
+      <c r="M14" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="N14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2373,10 +2373,10 @@
         <v>2012</v>
       </c>
       <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
         <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -2388,22 +2388,22 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J15" t="s">
+        <v>152</v>
+      </c>
+      <c r="K15" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" t="s">
         <v>153</v>
       </c>
-      <c r="K15" t="s">
-        <v>156</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="M15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
@@ -2414,10 +2414,10 @@
         <v>2010</v>
       </c>
       <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
         <v>72</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>51</v>
@@ -2429,25 +2429,25 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
+        <v>147</v>
+      </c>
+      <c r="K16" t="s">
         <v>148</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="L16" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="N16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2458,10 +2458,10 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" t="s">
         <v>75</v>
-      </c>
-      <c r="D17" t="s">
-        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>51</v>
@@ -2473,25 +2473,25 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K17" t="s">
         <v>175</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="M17" t="s">
         <v>177</v>
       </c>
-      <c r="M17" t="s">
-        <v>178</v>
-      </c>
       <c r="N17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2499,13 +2499,13 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
         <v>85</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
@@ -2514,14 +2514,14 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2529,13 +2529,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2544,10 +2544,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2555,13 +2555,13 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2570,22 +2570,22 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J20" t="s">
+        <v>200</v>
+      </c>
+      <c r="K20" t="s">
+        <v>199</v>
+      </c>
+      <c r="L20" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="K20" t="s">
-        <v>200</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>202</v>
-      </c>
       <c r="M20" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2596,13 +2596,13 @@
         <v>2012</v>
       </c>
       <c r="C21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" t="s">
         <v>94</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="F21" t="s">
         <v>19</v>
@@ -2611,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2625,13 +2625,13 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
         <v>99</v>
       </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
         <v>18</v>
@@ -2640,19 +2640,19 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2663,13 +2663,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
         <v>102</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -2678,25 +2678,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J23" t="s">
+        <v>147</v>
+      </c>
+      <c r="K23" t="s">
         <v>148</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="M23" t="s">
         <v>149</v>
       </c>
-      <c r="L23" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="M23" t="s">
-        <v>150</v>
-      </c>
       <c r="N23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2707,13 +2707,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -2722,25 +2722,25 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="J24" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" t="s">
+        <v>160</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="M24" t="s">
         <v>162</v>
       </c>
-      <c r="K24" t="s">
-        <v>161</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="M24" t="s">
-        <v>163</v>
-      </c>
       <c r="N24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2751,13 +2751,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
         <v>113</v>
       </c>
-      <c r="D25" t="s">
-        <v>114</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -2766,14 +2766,14 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2784,13 +2784,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
         <v>117</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2799,10 +2799,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="L26" s="15"/>
     </row>
@@ -2814,13 +2814,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" t="s">
         <v>122</v>
       </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -2829,13 +2829,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="L27" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2846,13 +2846,13 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" t="s">
         <v>126</v>
       </c>
-      <c r="D28" t="s">
-        <v>127</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
@@ -2861,25 +2861,25 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="J28" t="s">
+        <v>164</v>
+      </c>
+      <c r="K28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="M28" t="s">
         <v>165</v>
       </c>
-      <c r="K28" t="s">
-        <v>168</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="M28" t="s">
-        <v>166</v>
-      </c>
       <c r="N28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9682F3-0A36-4F72-A35A-59DCC6F03FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489F90B-04B4-4345-A406-F615AB950F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -159,6 +159,12 @@
         </r>
       </text>
     </comment>
+    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
+      <text/>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
+      <text/>
+    </comment>
     <comment ref="N22" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
       <text/>
     </comment>
@@ -167,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="219">
   <si>
     <t>section</t>
   </si>
@@ -788,9 +794,6 @@
     <t>Wilts FA Wildcats</t>
   </si>
   <si>
-    <t>So, what is Wildcats? Well, it’s non-competitive football for girls who want to give it a go for the very first time or want to play with other girls their own age. Most importantly, Wildcats is all about having loads of fun and meeting new amazing friends.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jaguars </t>
   </si>
   <si>
@@ -827,13 +830,41 @@
   </si>
   <si>
     <t>Mehdi  Najafi / Richie Lester</t>
+  </si>
+  <si>
+    <t>/images/sponsors/location.jpg</t>
+  </si>
+  <si>
+    <t>We don’t fit the mould – and we’re proud of it.</t>
+  </si>
+  <si>
+    <r>
+      <t>We’re not your typical estate agents – and that’s exactly the point.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Montserrat"/>
+      </rPr>
+      <t> We’re real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective – we’re a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://locationrealestate.co.uk/</t>
+  </si>
+  <si>
+    <t>/images/teams/jaguara/jaguars.jpg</t>
+  </si>
+  <si>
+    <t>Location Real Estate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1051,10 +1082,21 @@
       <name val="Poppins"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF011E41"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Montserrat"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1399,7 +1441,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1439,9 +1481,17 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1937,7 +1987,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>139</v>
@@ -2215,7 +2265,7 @@
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2233,16 +2283,16 @@
         <v>60</v>
       </c>
       <c r="J11" t="s">
+        <v>208</v>
+      </c>
+      <c r="K11" t="s">
         <v>209</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="M11" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="N11" t="s">
         <v>195</v>
@@ -2309,13 +2359,13 @@
         <v>67</v>
       </c>
       <c r="J13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K13" t="s">
         <v>206</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="17" t="s">
         <v>207</v>
-      </c>
-      <c r="L13" s="18" t="s">
-        <v>208</v>
       </c>
       <c r="N13" t="s">
         <v>185</v>
@@ -2524,12 +2574,12 @@
         <v>190</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
@@ -2544,10 +2594,25 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>88</v>
+      </c>
+      <c r="J19" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" t="s">
+        <v>213</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="M19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N19" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2581,11 +2646,9 @@
       <c r="K20" t="s">
         <v>199</v>
       </c>
-      <c r="L20" s="17" t="s">
-        <v>201</v>
-      </c>
+      <c r="L20" s="19"/>
       <c r="M20" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2615,6 +2678,9 @@
       </c>
       <c r="I21" s="2" t="s">
         <v>97</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489F90B-04B4-4345-A406-F615AB950F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF4E7A-8172-40AB-8B86-EDA64544E484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -463,9 +463,6 @@
     <t>Tuesday Evenings</t>
   </si>
   <si>
-    <t>The Lions are is a team for boys and girls, playing in the North Wilts Youth Football U13 Division 4 League</t>
-  </si>
-  <si>
     <t>wyfc.lions@gmail.com</t>
   </si>
   <si>
@@ -487,12 +484,6 @@
     <t>Monday Evenings</t>
   </si>
   <si>
-    <t>The Wolves are a team for boys and girls, playing in the North Wilts Youth Football U13 Division 4 League</t>
-  </si>
-  <si>
-    <t>Wasps is a team for boys and girls, playing in the North Wilts Youth Football U13 Division 5 League</t>
-  </si>
-  <si>
     <t>wyfc.wolves@gmail.com</t>
   </si>
   <si>
@@ -505,9 +496,6 @@
     <t>Wednesday Evenings</t>
   </si>
   <si>
-    <t>The Hurricanes are a team for boys and girls, playing in the North Wilts Youth Football U14 Division 1 League</t>
-  </si>
-  <si>
     <t>wyfc.hurricanes@gmail.com</t>
   </si>
   <si>
@@ -517,9 +505,6 @@
     <t>Darren Harvey</t>
   </si>
   <si>
-    <t>The Tornadoes a team for boys and girls, playing in the North Wilts Youth Football U14 Division 4 League</t>
-  </si>
-  <si>
     <t>wyfc.tornadoes@gmail.com</t>
   </si>
   <si>
@@ -532,9 +517,6 @@
     <t>Thursday Evenings</t>
   </si>
   <si>
-    <t>The Silverbacks are  a team for boys and girls, playing in the North Wilts Youth Football U15 Division 2 League</t>
-  </si>
-  <si>
     <t>wyfc.silverbacks@gmail.com</t>
   </si>
   <si>
@@ -542,9 +524,6 @@
   </si>
   <si>
     <t>Rob Zukovic</t>
-  </si>
-  <si>
-    <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football U16 Division 3 League</t>
   </si>
   <si>
     <t>wyfc.broncos@gmail.com</t>
@@ -854,10 +833,31 @@
     <t>https://locationrealestate.co.uk/</t>
   </si>
   <si>
-    <t>/images/teams/jaguara/jaguars.jpg</t>
-  </si>
-  <si>
     <t>Location Real Estate</t>
+  </si>
+  <si>
+    <t>/images/teams/jaguars/jaguars.jpg</t>
+  </si>
+  <si>
+    <t>Wasps is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Lions are is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Wolves are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Hurricanes are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Tornadoes a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Silverbacks are  a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football League</t>
   </si>
 </sst>
 </file>
@@ -1917,19 +1917,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M1" t="s">
         <v>133</v>
       </c>
-      <c r="K1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" t="s">
-        <v>140</v>
-      </c>
       <c r="N1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
@@ -1955,25 +1955,25 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="I2" t="s">
         <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="M2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="N2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1987,10 +1987,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1999,25 +1999,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="K3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="N3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2043,14 +2043,14 @@
         <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="10"/>
       <c r="N4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -2076,13 +2076,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="I5" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2108,13 +2108,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2146,7 +2146,7 @@
         <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>50</v>
@@ -2207,7 +2207,7 @@
         <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2239,19 +2239,19 @@
         <v>58</v>
       </c>
       <c r="J10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K10" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="L10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="N10" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
@@ -2265,7 +2265,7 @@
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2283,19 +2283,19 @@
         <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="K11" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="N11" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2327,7 +2327,7 @@
         <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2359,16 +2359,16 @@
         <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K13" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="N13" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
@@ -2400,19 +2400,19 @@
         <v>27</v>
       </c>
       <c r="J14" t="s">
+        <v>164</v>
+      </c>
+      <c r="K14" t="s">
         <v>171</v>
       </c>
-      <c r="K14" t="s">
-        <v>178</v>
-      </c>
       <c r="L14" s="16" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2444,16 +2444,16 @@
         <v>70</v>
       </c>
       <c r="J15" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K15" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="L15" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
@@ -2485,19 +2485,19 @@
         <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="N16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2529,19 +2529,19 @@
         <v>83</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M17" t="s">
+        <v>170</v>
+      </c>
+      <c r="N17" t="s">
         <v>177</v>
-      </c>
-      <c r="N17" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
@@ -2579,7 +2579,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
@@ -2594,25 +2594,25 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K19" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2641,14 +2641,14 @@
         <v>12</v>
       </c>
       <c r="J20" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L20" s="19"/>
       <c r="M20" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2674,13 +2674,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="L21" s="18" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2691,10 +2691,10 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" t="s">
         <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>99</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>95</v>
@@ -2706,19 +2706,19 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K22" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2729,13 +2729,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
         <v>101</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
@@ -2744,25 +2744,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J23" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="K23" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="M23" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="N23" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2773,13 +2773,13 @@
         <v>2011</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
         <v>18</v>
@@ -2788,25 +2788,25 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="M24" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N24" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2817,13 +2817,13 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
@@ -2832,14 +2832,14 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="L25" s="15"/>
       <c r="N25" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2850,13 +2850,13 @@
         <v>2010</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2865,10 +2865,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="L26" s="15"/>
     </row>
@@ -2880,13 +2880,13 @@
         <v>2009</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
         <v>18</v>
@@ -2895,13 +2895,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2912,10 +2912,10 @@
         <v>2007</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>95</v>
@@ -2927,25 +2927,25 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K28" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="M28" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="N28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BCF4E7A-8172-40AB-8B86-EDA64544E484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C03934F-EF09-4A1B-B034-F7FE937ABBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="220">
   <si>
     <t>section</t>
   </si>
@@ -737,9 +737,6 @@
     <t>/images/teams/tornadoes/tornadoes.jpg</t>
   </si>
   <si>
-    <t>/images/teams/blackcats/blackcats4.jpg |  /images/teams/blackcats/blackcats.jpg |  /images/teams/blackcats/blackcats5.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/mens/mens.jpg</t>
   </si>
   <si>
@@ -817,8 +814,38 @@
     <t>We don’t fit the mould – and we’re proud of it.</t>
   </si>
   <si>
+    <t>https://locationrealestate.co.uk/</t>
+  </si>
+  <si>
+    <t>Location Real Estate</t>
+  </si>
+  <si>
+    <t>/images/teams/jaguars/jaguars.jpg</t>
+  </si>
+  <si>
+    <t>Wasps is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Lions are is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Wolves are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Hurricanes are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Tornadoes a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Silverbacks are  a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
     <r>
-      <t>We’re not your typical estate agents – and that’s exactly the point.</t>
+      <t xml:space="preserve">Not your typical estate agents,  and that's exactly the point. </t>
     </r>
     <r>
       <rPr>
@@ -826,38 +853,14 @@
         <color theme="1"/>
         <rFont val="Montserrat"/>
       </rPr>
-      <t> We’re real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective – we’re a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
+      <t>We’re real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
     </r>
   </si>
   <si>
-    <t>https://locationrealestate.co.uk/</t>
-  </si>
-  <si>
-    <t>Location Real Estate</t>
-  </si>
-  <si>
-    <t>/images/teams/jaguars/jaguars.jpg</t>
-  </si>
-  <si>
-    <t>Wasps is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
-  </si>
-  <si>
-    <t>The Lions are is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
-  </si>
-  <si>
-    <t>The Wolves are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
-  </si>
-  <si>
-    <t>The Hurricanes are a team for boys and girls, playing in the North Wilts Youth Football  League</t>
-  </si>
-  <si>
-    <t>The Tornadoes a team for boys and girls, playing in the North Wilts Youth Football League</t>
-  </si>
-  <si>
-    <t>The Silverbacks are  a team for boys and girls, playing in the North Wilts Youth Football  League</t>
-  </si>
-  <si>
-    <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+    <t>jaguars@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>/images/teams/blackcats/blackcats7.jpg |  /images/teams/blackcats/blackcats6.jpg |  /images/teams/blackcats/blackcats2.jpg</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +1976,7 @@
         <v>137</v>
       </c>
       <c r="N2" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -1987,7 +1990,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>132</v>
@@ -2114,7 +2117,7 @@
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2146,7 +2149,7 @@
         <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2265,7 +2268,7 @@
         <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2283,19 +2286,19 @@
         <v>60</v>
       </c>
       <c r="J11" t="s">
+        <v>200</v>
+      </c>
+      <c r="K11" t="s">
         <v>201</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="M11" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="N11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2327,7 +2330,7 @@
         <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2359,13 +2362,13 @@
         <v>67</v>
       </c>
       <c r="J13" t="s">
+        <v>197</v>
+      </c>
+      <c r="K13" t="s">
         <v>198</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="17" t="s">
         <v>199</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>200</v>
       </c>
       <c r="N13" t="s">
         <v>178</v>
@@ -2497,7 +2500,7 @@
         <v>142</v>
       </c>
       <c r="N16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2571,7 +2574,7 @@
       </c>
       <c r="L18" s="12"/>
       <c r="N18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
@@ -2579,7 +2582,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
@@ -2594,25 +2597,25 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="J19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M19" t="s">
+        <v>207</v>
+      </c>
+      <c r="N19" t="s">
         <v>209</v>
-      </c>
-      <c r="N19" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2641,14 +2644,14 @@
         <v>12</v>
       </c>
       <c r="J20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L20" s="19"/>
       <c r="M20" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2674,13 +2677,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>96</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -2706,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>99</v>
@@ -2718,7 +2721,7 @@
         <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2744,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>103</v>
@@ -2762,7 +2765,7 @@
         <v>142</v>
       </c>
       <c r="N23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2788,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>107</v>
@@ -2832,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>110</v>
@@ -2865,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>114</v>
@@ -2895,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>117</v>
@@ -2945,7 +2948,7 @@
         <v>158</v>
       </c>
       <c r="N28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C03934F-EF09-4A1B-B034-F7FE937ABBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860BD015-5A8F-4F81-A9C6-B33DC3570968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -844,6 +844,12 @@
     <t>The Broncos are a team for boys and girls, playing in the North Wilts Youth Football League</t>
   </si>
   <si>
+    <t>jaguars@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>/images/teams/blackcats/blackcats7.jpg |  /images/teams/blackcats/blackcats6.jpg |  /images/teams/blackcats/blackcats4.jpg</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Not your typical estate agents,  and that's exactly the point. </t>
     </r>
@@ -853,14 +859,8 @@
         <color theme="1"/>
         <rFont val="Montserrat"/>
       </rPr>
-      <t>We’re real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
+      <t>We're real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
     </r>
-  </si>
-  <si>
-    <t>jaguars@wwfc.org.uk</t>
-  </si>
-  <si>
-    <t>/images/teams/blackcats/blackcats7.jpg |  /images/teams/blackcats/blackcats6.jpg |  /images/teams/blackcats/blackcats2.jpg</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +1976,7 @@
         <v>137</v>
       </c>
       <c r="N2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -2600,7 +2600,7 @@
         <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J19" t="s">
         <v>208</v>
@@ -2609,7 +2609,7 @@
         <v>205</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s">
         <v>207</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860BD015-5A8F-4F81-A9C6-B33DC3570968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E447FE-CB06-4597-A438-604791B3D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -145,6 +145,9 @@
         </r>
       </text>
     </comment>
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
+      <text/>
+    </comment>
     <comment ref="N18" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
       <text>
         <r>
@@ -158,9 +161,6 @@
           <t>William Crow</t>
         </r>
       </text>
-    </comment>
-    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
-      <text/>
     </comment>
     <comment ref="N19" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
       <text/>
@@ -1444,7 +1444,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1469,9 +1469,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2291,7 +2288,7 @@
       <c r="K11" t="s">
         <v>201</v>
       </c>
-      <c r="L11" s="17" t="s">
+      <c r="L11" s="16" t="s">
         <v>202</v>
       </c>
       <c r="M11" s="2" t="s">
@@ -2367,7 +2364,7 @@
       <c r="K13" t="s">
         <v>198</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="16" t="s">
         <v>199</v>
       </c>
       <c r="N13" t="s">
@@ -2408,7 +2405,7 @@
       <c r="K14" t="s">
         <v>171</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L14" s="15" t="s">
         <v>165</v>
       </c>
       <c r="M14" s="2" t="s">
@@ -2493,7 +2490,7 @@
       <c r="K16" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="12" t="s">
         <v>144</v>
       </c>
       <c r="M16" s="2" t="s">
@@ -2547,7 +2544,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2572,12 +2569,23 @@
       <c r="I18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L18" s="12"/>
+      <c r="J18" t="s">
+        <v>208</v>
+      </c>
+      <c r="K18" t="s">
+        <v>205</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M18" t="s">
+        <v>207</v>
+      </c>
       <c r="N18" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -2601,18 +2609,6 @@
       </c>
       <c r="I19" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="J19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K19" t="s">
-        <v>205</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="M19" t="s">
-        <v>207</v>
       </c>
       <c r="N19" t="s">
         <v>209</v>
@@ -2649,7 +2645,7 @@
       <c r="K20" t="s">
         <v>191</v>
       </c>
-      <c r="L20" s="19"/>
+      <c r="L20" s="18"/>
       <c r="M20" s="2" t="s">
         <v>195</v>
       </c>
@@ -2682,7 +2678,7 @@
       <c r="I21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L21" s="18" t="s">
+      <c r="L21" s="17" t="s">
         <v>206</v>
       </c>
     </row>
@@ -2758,7 +2754,7 @@
       <c r="K23" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="13" t="s">
         <v>144</v>
       </c>
       <c r="M23" t="s">
@@ -2802,7 +2798,7 @@
       <c r="K24" t="s">
         <v>153</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="13" t="s">
         <v>159</v>
       </c>
       <c r="M24" t="s">
@@ -2840,7 +2836,7 @@
       <c r="I25" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L25" s="15"/>
+      <c r="L25" s="14"/>
       <c r="N25" t="s">
         <v>181</v>
       </c>
@@ -2873,7 +2869,7 @@
       <c r="I26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="L26" s="15"/>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -2903,7 +2899,7 @@
       <c r="I27" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="13" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2941,7 +2937,7 @@
       <c r="K28" t="s">
         <v>160</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="13" t="s">
         <v>161</v>
       </c>
       <c r="M28" t="s">
@@ -2953,7 +2949,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="1"/>
-      <c r="L29" s="15"/>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E447FE-CB06-4597-A438-604791B3D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A23E287-4DC3-4E9D-AE69-120D9A8B40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
       <text>
         <r>
           <rPr>
@@ -74,10 +74,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
       <text/>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
       <text>
         <r>
           <rPr>
@@ -91,13 +91,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
+    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
       <text/>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
       <text/>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
+    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
+    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
           <rPr>
@@ -145,10 +145,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
+    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
       <text/>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
+    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
       <text>
         <r>
           <rPr>
@@ -162,10 +162,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
       <text/>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
+    <comment ref="N23" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
       <text/>
     </comment>
   </commentList>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="224">
   <si>
     <t>section</t>
   </si>
@@ -861,6 +861,18 @@
       </rPr>
       <t>We're real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
     </r>
+  </si>
+  <si>
+    <t>Rebels</t>
+  </si>
+  <si>
+    <t>Jack Morement</t>
+  </si>
+  <si>
+    <t>The Rebels are a newly formed team, starting at u8 and playing 5v5 Footnall</t>
+  </si>
+  <si>
+    <t>rebels@wwfc.org.uk</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -2020,40 +2032,38 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>220</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>221</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>122</v>
+      <c r="H4" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="10"/>
-      <c r="N4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2061,63 +2071,64 @@
         <v>2017</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
+      <c r="H5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="10"/>
       <c r="N5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>43</v>
+      <c r="H6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
       </c>
       <c r="N6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2125,74 +2136,77 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
+      <c r="H7" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
       <c r="B9">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -2201,13 +2215,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" t="s">
-        <v>173</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2218,10 +2229,10 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
@@ -2233,28 +2244,16 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>150</v>
-      </c>
-      <c r="K10" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" t="s">
-        <v>151</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2262,10 +2261,10 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2277,28 +2276,28 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="J11" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K11" t="s">
-        <v>201</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>202</v>
+        <v>149</v>
+      </c>
+      <c r="L11" t="s">
+        <v>151</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2306,10 +2305,10 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2320,28 +2319,40 @@
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>64</v>
+      <c r="H12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>200</v>
+      </c>
+      <c r="K12" t="s">
+        <v>201</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="N12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2353,25 +2364,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J13" t="s">
-        <v>197</v>
-      </c>
-      <c r="K13" t="s">
-        <v>198</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>199</v>
+        <v>64</v>
       </c>
       <c r="N13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2379,13 +2381,13 @@
         <v>2013</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1">
-        <v>19</v>
+        <v>66</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -2393,84 +2395,84 @@
       <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>32</v>
+      <c r="H14" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J14" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>166</v>
+        <v>198</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="N14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="E15" s="1">
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>78</v>
+      <c r="H15" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="J15" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K15" t="s">
-        <v>148</v>
-      </c>
-      <c r="L15" t="s">
-        <v>146</v>
+        <v>171</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="N15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -2479,28 +2481,25 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K16" t="s">
-        <v>141</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>144</v>
+        <v>148</v>
+      </c>
+      <c r="L16" t="s">
+        <v>146</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="N16" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2508,10 +2507,10 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>51</v>
@@ -2523,109 +2522,124 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="J17" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="K17" t="s">
-        <v>168</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="M17" t="s">
-        <v>170</v>
+        <v>141</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>2010</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J18" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="K18" t="s">
-        <v>205</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>219</v>
+        <v>168</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>169</v>
       </c>
       <c r="M18" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="N18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>194</v>
+      <c r="H19" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>217</v>
+        <v>88</v>
+      </c>
+      <c r="J19" t="s">
+        <v>208</v>
+      </c>
+      <c r="K19" t="s">
+        <v>205</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="M19" t="s">
+        <v>207</v>
       </c>
       <c r="N19" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2634,55 +2648,52 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J21" t="s">
         <v>192</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K21" t="s">
         <v>191</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="2" t="s">
+      <c r="L21" s="18"/>
+      <c r="M21" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>2012</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2690,37 +2701,31 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>210</v>
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>211</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J22" t="s">
-        <v>97</v>
-      </c>
-      <c r="K22" t="s">
-        <v>172</v>
-      </c>
-      <c r="N22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2728,40 +2733,34 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>212</v>
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="K23" t="s">
-        <v>141</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="N23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2769,46 +2768,46 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="M24" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -2816,29 +2815,40 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="14"/>
+        <v>107</v>
+      </c>
+      <c r="J25" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="M25" t="s">
+        <v>155</v>
+      </c>
       <c r="N25" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2846,16 +2856,16 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2864,95 +2874,125 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="N26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
       <c r="B27">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="L27" s="14"/>
+    </row>
+    <row r="28" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
       <c r="B28">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29">
+        <v>2007</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J29" t="s">
         <v>157</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K29" t="s">
         <v>160</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="L29" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M29" t="s">
         <v>158</v>
       </c>
-      <c r="N28" t="s">
+      <c r="N29" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E29" s="1"/>
-      <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
+      <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
@@ -3080,41 +3120,45 @@
     <row r="72" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E72" s="1"/>
     </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E73" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I14" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
-    <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
-    <hyperlink ref="I8" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
-    <hyperlink ref="I9" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
-    <hyperlink ref="I10" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
-    <hyperlink ref="I12" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
-    <hyperlink ref="I13" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
-    <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
-    <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
-    <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
-    <hyperlink ref="I18" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
-    <hyperlink ref="I19" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
-    <hyperlink ref="I20" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
-    <hyperlink ref="I21" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
-    <hyperlink ref="I22" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
-    <hyperlink ref="I23" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
-    <hyperlink ref="I24" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
-    <hyperlink ref="I25" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
-    <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
-    <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
-    <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
+    <hyperlink ref="I15" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+    <hyperlink ref="I5" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
+    <hyperlink ref="I7" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
+    <hyperlink ref="I9" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
+    <hyperlink ref="I10" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
+    <hyperlink ref="I11" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
+    <hyperlink ref="I13" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
+    <hyperlink ref="I14" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
+    <hyperlink ref="I16" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
+    <hyperlink ref="I17" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
+    <hyperlink ref="I18" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
+    <hyperlink ref="I19" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
+    <hyperlink ref="I20" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
+    <hyperlink ref="I21" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
+    <hyperlink ref="I22" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
+    <hyperlink ref="I23" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
+    <hyperlink ref="I24" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
+    <hyperlink ref="I25" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
+    <hyperlink ref="I26" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
+    <hyperlink ref="I27" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
+    <hyperlink ref="I28" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
+    <hyperlink ref="I29" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
     <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
-    <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
-    <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
-    <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
-    <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
-    <hyperlink ref="M20" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
-    <hyperlink ref="M11" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
+    <hyperlink ref="M16" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
+    <hyperlink ref="M11" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
+    <hyperlink ref="M17" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
+    <hyperlink ref="M15" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
+    <hyperlink ref="M21" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
+    <hyperlink ref="M12" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
+    <hyperlink ref="I4" r:id="rId30" xr:uid="{C04DA833-5EA0-4EC2-B81E-13611A882C0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId30"/>
-  <legacyDrawing r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
+  <legacyDrawing r:id="rId32"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -3122,7 +3166,7 @@
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>F18:F1048576 I7 F1:F16</xm:sqref>
+          <xm:sqref>F19:F1048576 I8 F1:F17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A23E287-4DC3-4E9D-AE69-120D9A8B40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E447FE-CB06-4597-A438-604791B3D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -50,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
+    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
       <text>
         <r>
           <rPr>
@@ -74,10 +74,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
       <text/>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
       <text>
         <r>
           <rPr>
@@ -91,13 +91,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
+    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
       <text/>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
       <text/>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
+    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
           <rPr>
@@ -145,10 +145,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
       <text/>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
       <text>
         <r>
           <rPr>
@@ -162,10 +162,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
+    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
       <text/>
     </comment>
-    <comment ref="N23" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
+    <comment ref="N22" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
       <text/>
     </comment>
   </commentList>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="220">
   <si>
     <t>section</t>
   </si>
@@ -861,18 +861,6 @@
       </rPr>
       <t>We're real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
     </r>
-  </si>
-  <si>
-    <t>Rebels</t>
-  </si>
-  <si>
-    <t>Jack Morement</t>
-  </si>
-  <si>
-    <t>The Rebels are a newly formed team, starting at u8 and playing 5v5 Footnall</t>
-  </si>
-  <si>
-    <t>rebels@wwfc.org.uk</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -2032,38 +2020,40 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C4" t="s">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>222</v>
+      <c r="H4" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="N4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -2071,64 +2061,63 @@
         <v>2017</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="10"/>
+      <c r="H5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
+      <c r="H6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2136,77 +2125,74 @@
         <v>2016</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>43</v>
+      <c r="H7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
       </c>
       <c r="N7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="42" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -2215,10 +2201,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
+      </c>
+      <c r="N9" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2229,10 +2218,10 @@
         <v>2014</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
@@ -2244,16 +2233,28 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="J10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" t="s">
+        <v>149</v>
+      </c>
+      <c r="L10" t="s">
+        <v>151</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="N10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -2261,10 +2262,10 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>204</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>35</v>
@@ -2276,28 +2277,28 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="J11" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K11" t="s">
-        <v>149</v>
-      </c>
-      <c r="L11" t="s">
-        <v>151</v>
+        <v>201</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>202</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="N11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -2305,10 +2306,10 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>35</v>
@@ -2319,40 +2320,28 @@
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" t="s">
-        <v>200</v>
-      </c>
-      <c r="K12" t="s">
-        <v>201</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>203</v>
+      <c r="H12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="N12" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>35</v>
@@ -2364,16 +2353,25 @@
         <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
+      </c>
+      <c r="J13" t="s">
+        <v>197</v>
+      </c>
+      <c r="K13" t="s">
+        <v>198</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="N13" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2381,13 +2379,13 @@
         <v>2013</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="E14" s="1">
+        <v>19</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -2395,84 +2393,84 @@
       <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>79</v>
+      <c r="H14" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="K14" t="s">
-        <v>198</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>199</v>
+        <v>171</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="N14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="45" x14ac:dyDescent="0.7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B15">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="1">
-        <v>19</v>
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>32</v>
+      <c r="H15" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="J15" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>165</v>
+        <v>148</v>
+      </c>
+      <c r="L15" t="s">
+        <v>146</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
         <v>11</v>
@@ -2481,25 +2479,28 @@
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K16" t="s">
-        <v>148</v>
-      </c>
-      <c r="L16" t="s">
-        <v>146</v>
+        <v>141</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="N16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2507,10 +2508,10 @@
         <v>2010</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>51</v>
@@ -2522,124 +2523,109 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="K17" t="s">
-        <v>141</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>142</v>
+        <v>168</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M17" t="s">
+        <v>170</v>
       </c>
       <c r="N17" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18">
-        <v>2010</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="K18" t="s">
-        <v>168</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>169</v>
+        <v>205</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>219</v>
       </c>
       <c r="M18" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="N18" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="D19" t="s">
         <v>85</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>87</v>
+      <c r="H19" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K19" t="s">
-        <v>205</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="M19" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="N19" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
         <v>11</v>
@@ -2648,52 +2634,55 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="N20" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="J20" t="s">
+        <v>192</v>
+      </c>
+      <c r="K20" t="s">
+        <v>191</v>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>2012</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" t="s">
-        <v>192</v>
-      </c>
-      <c r="K21" t="s">
-        <v>191</v>
-      </c>
-      <c r="L21" s="18"/>
-      <c r="M21" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2701,31 +2690,37 @@
         <v>2012</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>211</v>
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="J22" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" t="s">
+        <v>172</v>
+      </c>
+      <c r="N22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2733,34 +2728,40 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>210</v>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J23" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
+        <v>141</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="M23" t="s">
+        <v>142</v>
       </c>
       <c r="N23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
@@ -2768,46 +2769,46 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="K24" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="M24" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="N24" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -2815,40 +2816,29 @@
         <v>2011</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" t="s">
-        <v>154</v>
-      </c>
-      <c r="K25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="M25" t="s">
-        <v>155</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="L25" s="14"/>
       <c r="N25" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2856,16 +2846,16 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
@@ -2874,125 +2864,95 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L26" s="14"/>
-      <c r="N26" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
       <c r="B27">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
       <c r="B28">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>216</v>
+      <c r="H28" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
+      </c>
+      <c r="J28" t="s">
+        <v>157</v>
+      </c>
+      <c r="K28" t="s">
+        <v>160</v>
       </c>
       <c r="L28" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29">
-        <v>2007</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J29" t="s">
-        <v>157</v>
-      </c>
-      <c r="K29" t="s">
-        <v>160</v>
-      </c>
-      <c r="L29" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M28" t="s">
         <v>158</v>
       </c>
-      <c r="N29" t="s">
+      <c r="N28" t="s">
         <v>183</v>
       </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E29" s="1"/>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E30" s="1"/>
-      <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E31" s="1"/>
@@ -3120,45 +3080,41 @@
     <row r="72" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E72" s="1"/>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E73" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I15" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
-    <hyperlink ref="I5" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
-    <hyperlink ref="I7" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
-    <hyperlink ref="I9" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
-    <hyperlink ref="I10" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
-    <hyperlink ref="I11" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
-    <hyperlink ref="I13" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
-    <hyperlink ref="I14" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
-    <hyperlink ref="I16" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
-    <hyperlink ref="I17" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
-    <hyperlink ref="I18" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
-    <hyperlink ref="I19" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
-    <hyperlink ref="I20" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
-    <hyperlink ref="I21" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
-    <hyperlink ref="I22" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
-    <hyperlink ref="I23" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
-    <hyperlink ref="I24" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
-    <hyperlink ref="I25" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
-    <hyperlink ref="I26" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
-    <hyperlink ref="I27" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
-    <hyperlink ref="I28" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
-    <hyperlink ref="I29" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
+    <hyperlink ref="I14" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
+    <hyperlink ref="I6" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
+    <hyperlink ref="I8" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
+    <hyperlink ref="I9" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
+    <hyperlink ref="I10" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
+    <hyperlink ref="I12" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
+    <hyperlink ref="I13" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
+    <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
+    <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
+    <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
+    <hyperlink ref="I18" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
+    <hyperlink ref="I19" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
+    <hyperlink ref="I20" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
+    <hyperlink ref="I21" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
+    <hyperlink ref="I22" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
+    <hyperlink ref="I23" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
+    <hyperlink ref="I24" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
+    <hyperlink ref="I25" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
+    <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
+    <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
+    <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
     <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
-    <hyperlink ref="M16" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
-    <hyperlink ref="M11" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
-    <hyperlink ref="M17" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
-    <hyperlink ref="M15" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
-    <hyperlink ref="M21" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
-    <hyperlink ref="M12" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
-    <hyperlink ref="I4" r:id="rId30" xr:uid="{C04DA833-5EA0-4EC2-B81E-13611A882C0E}"/>
+    <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
+    <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
+    <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
+    <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
+    <hyperlink ref="M20" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
+    <hyperlink ref="M11" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId31"/>
-  <legacyDrawing r:id="rId32"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId30"/>
+  <legacyDrawing r:id="rId31"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -3166,7 +3122,7 @@
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>F19:F1048576 I8 F1:F17</xm:sqref>
+          <xm:sqref>F18:F1048576 I7 F1:F16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>
